--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$158</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$165</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="1013">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1590,6 +1590,12 @@
     <t xml:space="preserve">Nearly 11 months of military presence in Washington with no end date</t>
   </si>
   <si>
+    <t xml:space="preserve">Jul 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 11</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -2998,6 +3004,57 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.bostonglobe.com/2026/07/07/nation/trump-presidency-live-updates/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the same day, a Florida airport and a Tennessee bridge are renamed after Trump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/donald-trump/palm-beach-international-airport-tennessee-bridge-renamed-rcna353784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 10, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump restarts war with Iran and plays nice(ish) with Nato | Politics Weekly America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/politics/video/2026/jul/10/trump-restarts-war-with-iran-and-plays-niceish-with-nato-politics-weekly-america</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crews draining the Lincoln Memorial Reflecting Pool again as part of troubled revamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/crews-draining-lincoln-memorial-reflecting-pool-part-trumps-134656303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PBS NewsHour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump fires election commission members in latest attempt to control voting process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/show/trump-fires-election-commission-members-in-latest-attempt-to-control-voting-process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal officials refusing to release name of ICE officer who fatally shot Lorenzo Salgado Araujo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/politics/federal-officials-refusing-to-release-name-of-ice-officer-who-fatally-shot-lorenzo-salgado-araujo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justice Department subpoenas New York Times reporters over Air Force One reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.npr.org/2026/07/11/g-s1-133160/justice-department-subpoenas-new-york-times-reporters-over-air-force-one-reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 11, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judge tosses remaining Jan. 6 Proud Boys convictions after DOJ request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/justice-department/judge-grants-doj-request-toss-remaining-jan-6-convictions-proud-boys-rcna385952</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -3145,8 +3202,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3170,19 +3231,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3475,3168 +3536,3266 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F165"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="4" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="5" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="5" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="5" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="5" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+    <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+    <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="4" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="4" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="4" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="4" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="4" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="5" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="5" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="5" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+    <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="5" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+    <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="4" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+    <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F25" s="4" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="4" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="5" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+    <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="5" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="F29" s="4" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="F30" s="4" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
+    <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F31" s="4" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+    <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="4" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+    <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="5" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="5" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
+    <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="5" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="5" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
+    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F37" s="3" t="n">
+      <c r="F37" s="4" t="n">
         <v>35</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
+    <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="F38" s="4" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+    <row r="39" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="5" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
+    <row r="40" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="5" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="5" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
+    <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="F42" s="4" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+    <row r="43" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="5" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+    <row r="44" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="5" t="n">
         <v>42</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
+    <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="F45" s="4" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="s">
+    <row r="46" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="F46" s="4" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="F47" s="4" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
+    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="F48" s="5" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
+    <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="F49" s="3" t="n">
+      <c r="F49" s="4" t="n">
         <v>47</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
+    <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="F50" s="5" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="F51" s="4" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
+    <row r="52" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="F52" s="3" t="n">
+      <c r="F52" s="4" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
+    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="F53" s="5" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
+    <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="F54" s="5" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="s">
+    <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F55" s="3" t="n">
+      <c r="F55" s="4" t="n">
         <v>53</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+    <row r="56" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="5" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="s">
+    <row r="57" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="F57" s="3" t="n">
+      <c r="F57" s="4" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="s">
+    <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E58" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F58" s="3" t="n">
+      <c r="F58" s="4" t="n">
         <v>56</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
+    <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F59" s="5" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="s">
+    <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F60" s="3" t="n">
+      <c r="F60" s="4" t="n">
         <v>58</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
+    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="E61" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="F61" s="5" t="n">
         <v>59</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="3" t="s">
+    <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E62" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="F62" s="3" t="n">
+      <c r="F62" s="4" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="s">
+    <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="F63" s="5" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="s">
+    <row r="64" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="F64" s="3" t="n">
+      <c r="F64" s="4" t="n">
         <v>62</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="3" t="s">
+    <row r="65" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="F65" s="3" t="n">
+      <c r="F65" s="4" t="n">
         <v>63</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+    <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="E66" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="F66" s="5" t="n">
         <v>64</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="3" t="s">
+    <row r="67" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="F67" s="3" t="n">
+      <c r="F67" s="4" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3" t="s">
+    <row r="68" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F68" s="3" t="n">
+      <c r="F68" s="4" t="n">
         <v>66</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
+    <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="E69" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="F69" s="5" t="n">
         <v>67</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="s">
+    <row r="70" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="E70" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="F70" s="5" t="n">
         <v>68</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="s">
+    <row r="71" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="E71" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="F71" s="5" t="n">
         <v>69</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="3" t="s">
+    <row r="72" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E72" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="F72" s="3" t="n">
+      <c r="F72" s="4" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
+    <row r="73" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E73" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="F73" s="3" t="n">
+      <c r="F73" s="4" t="n">
         <v>71</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
+    <row r="74" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="E74" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="5" t="n">
         <v>72</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="3" t="s">
+    <row r="75" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E75" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="F75" s="3" t="n">
+      <c r="F75" s="4" t="n">
         <v>73</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
+    <row r="76" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="E76" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="5" t="n">
         <v>74</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3" t="s">
+    <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E77" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="F77" s="3" t="n">
+      <c r="F77" s="4" t="n">
         <v>75</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
+    <row r="78" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="E78" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="F78" s="5" t="n">
         <v>76</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
+    <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="F79" s="3" t="n">
+      <c r="F79" s="4" t="n">
         <v>77</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="s">
+    <row r="80" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="F80" s="3" t="n">
+      <c r="F80" s="4" t="n">
         <v>78</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="s">
+    <row r="81" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="E81" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="F81" s="5" t="n">
         <v>79</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="3" t="s">
+    <row r="82" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E82" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="F82" s="3" t="n">
+      <c r="F82" s="4" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="s">
+    <row r="83" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="E83" s="4" t="s">
+      <c r="E83" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="F83" s="5" t="n">
         <v>81</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="3" t="s">
+    <row r="84" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E84" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="F84" s="3" t="n">
+      <c r="F84" s="4" t="n">
         <v>82</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="s">
+    <row r="85" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="E85" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="F85" s="5" t="n">
         <v>83</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="s">
+    <row r="86" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="E86" s="4" t="s">
+      <c r="E86" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="5" t="n">
         <v>84</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
+    <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="E87" s="4" t="s">
+      <c r="E87" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F87" s="5" t="n">
         <v>85</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
+    <row r="88" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D88" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="E88" s="4" t="s">
+      <c r="E88" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="F88" s="5" t="n">
         <v>86</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="s">
+    <row r="89" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D89" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="E89" s="4" t="s">
+      <c r="E89" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="F89" s="4" t="n">
+      <c r="F89" s="5" t="n">
         <v>87</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="s">
+    <row r="90" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D90" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="E90" s="4" t="s">
+      <c r="E90" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="F90" s="4" t="n">
+      <c r="F90" s="5" t="n">
         <v>88</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="s">
+    <row r="91" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="E91" s="4" t="s">
+      <c r="E91" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="F91" s="4" t="n">
+      <c r="F91" s="5" t="n">
         <v>89</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="3" t="s">
+    <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="E92" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F92" s="3" t="n">
+      <c r="F92" s="4" t="n">
         <v>90</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="3" t="s">
+    <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="E93" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F93" s="3" t="n">
+      <c r="F93" s="4" t="n">
         <v>91</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="3" t="s">
+    <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="E94" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="F94" s="3" t="n">
+      <c r="F94" s="4" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="3" t="s">
+    <row r="95" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E95" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="F95" s="3" t="n">
+      <c r="F95" s="4" t="n">
         <v>93</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="3" t="s">
+    <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="E96" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="F96" s="3" t="n">
+      <c r="F96" s="4" t="n">
         <v>94</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="3" t="s">
+    <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="E97" s="3" t="s">
+      <c r="E97" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="F97" s="3" t="n">
+      <c r="F97" s="4" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3" t="s">
+    <row r="98" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="E98" s="3" t="s">
+      <c r="E98" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F98" s="3" t="n">
+      <c r="F98" s="4" t="n">
         <v>96</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="s">
+    <row r="99" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="E99" s="4" t="s">
+      <c r="E99" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="F99" s="4" t="n">
+      <c r="F99" s="5" t="n">
         <v>97</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="4" t="s">
+    <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="D100" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="E100" s="4" t="s">
+      <c r="E100" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="F100" s="4" t="n">
+      <c r="F100" s="5" t="n">
         <v>98</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="4" t="s">
+    <row r="101" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="D101" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="E101" s="4" t="s">
+      <c r="E101" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="F101" s="4" t="n">
+      <c r="F101" s="5" t="n">
         <v>99</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="4" t="s">
+    <row r="102" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="D102" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="E102" s="4" t="s">
+      <c r="E102" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="F102" s="4" t="n">
+      <c r="F102" s="5" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="3" t="s">
+    <row r="103" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="E103" s="3" t="s">
+      <c r="E103" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="F103" s="3" t="n">
+      <c r="F103" s="4" t="n">
         <v>101</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="3" t="s">
+    <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C104" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="D104" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="E104" s="3" t="s">
+      <c r="E104" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="F104" s="3" t="n">
+      <c r="F104" s="4" t="n">
         <v>102</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="3" t="s">
+    <row r="105" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="D105" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="E105" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F105" s="3" t="n">
+      <c r="F105" s="4" t="n">
         <v>103</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="3" t="s">
+    <row r="106" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D106" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="E106" s="3" t="s">
+      <c r="E106" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="F106" s="3" t="n">
+      <c r="F106" s="4" t="n">
         <v>104</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="3" t="s">
+    <row r="107" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="D107" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="E107" s="3" t="s">
+      <c r="E107" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="F107" s="3" t="n">
+      <c r="F107" s="4" t="n">
         <v>105</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="4" t="s">
+    <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D108" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="E108" s="4" t="s">
+      <c r="E108" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="F108" s="4" t="n">
+      <c r="F108" s="5" t="n">
         <v>106</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="4" t="s">
+    <row r="109" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D109" s="4" t="s">
+      <c r="D109" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="E109" s="4" t="s">
+      <c r="E109" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="F109" s="4" t="n">
+      <c r="F109" s="5" t="n">
         <v>107</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="4" t="s">
+    <row r="110" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D110" s="4" t="s">
+      <c r="D110" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="E110" s="4" t="s">
+      <c r="E110" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="F110" s="4" t="n">
+      <c r="F110" s="5" t="n">
         <v>108</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="4" t="s">
+    <row r="111" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D111" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="E111" s="4" t="s">
+      <c r="E111" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="F111" s="4" t="n">
+      <c r="F111" s="5" t="n">
         <v>109</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="4" t="s">
+    <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="D112" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="E112" s="4" t="s">
+      <c r="E112" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="F112" s="4" t="n">
+      <c r="F112" s="5" t="n">
         <v>110</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="3" t="s">
+    <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C113" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D113" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="E113" s="3" t="s">
+      <c r="E113" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="F113" s="3" t="n">
+      <c r="F113" s="4" t="n">
         <v>111</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="3" t="s">
+    <row r="114" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C114" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D114" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="E114" s="3" t="s">
+      <c r="E114" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="F114" s="3" t="n">
+      <c r="F114" s="4" t="n">
         <v>112</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="3" t="s">
+    <row r="115" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C115" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D115" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="E115" s="3" t="s">
+      <c r="E115" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="F115" s="3" t="n">
+      <c r="F115" s="4" t="n">
         <v>113</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="3" t="s">
+    <row r="116" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D116" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="E116" s="3" t="s">
+      <c r="E116" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="F116" s="3" t="n">
+      <c r="F116" s="4" t="n">
         <v>114</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="3" t="s">
+    <row r="117" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="D117" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="E117" s="3" t="s">
+      <c r="E117" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="F117" s="3" t="n">
+      <c r="F117" s="4" t="n">
         <v>115</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="4" t="s">
+    <row r="118" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="D118" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="E118" s="4" t="s">
+      <c r="E118" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="F118" s="4" t="n">
+      <c r="F118" s="5" t="n">
         <v>116</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="4" t="s">
+    <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B119" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D119" s="4" t="s">
+      <c r="D119" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="E119" s="4" t="s">
+      <c r="E119" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="F119" s="4" t="n">
+      <c r="F119" s="5" t="n">
         <v>117</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="4" t="s">
+    <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D120" s="4" t="s">
+      <c r="D120" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="E120" s="4" t="s">
+      <c r="E120" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="F120" s="4" t="n">
+      <c r="F120" s="5" t="n">
         <v>118</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="4" t="s">
+    <row r="121" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C121" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D121" s="4" t="s">
+      <c r="D121" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="E121" s="4" t="s">
+      <c r="E121" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="F121" s="4" t="n">
+      <c r="F121" s="5" t="n">
         <v>119</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="4" t="s">
+    <row r="122" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="C122" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D122" s="4" t="s">
+      <c r="D122" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="E122" s="4" t="s">
+      <c r="E122" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="F122" s="4" t="n">
+      <c r="F122" s="5" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="3" t="s">
+    <row r="123" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="C123" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="D123" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="E123" s="3" t="s">
+      <c r="E123" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="F123" s="3" t="n">
+      <c r="F123" s="4" t="n">
         <v>121</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="3" t="s">
+    <row r="124" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="C124" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="D124" s="3" t="s">
+      <c r="D124" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="E124" s="3" t="s">
+      <c r="E124" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="F124" s="3" t="n">
+      <c r="F124" s="4" t="n">
         <v>122</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="3" t="s">
+    <row r="125" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="C125" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D125" s="3" t="s">
+      <c r="D125" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="E125" s="3" t="s">
+      <c r="E125" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="F125" s="3" t="n">
+      <c r="F125" s="4" t="n">
         <v>123</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="3" t="s">
+    <row r="126" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="C126" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D126" s="3" t="s">
+      <c r="D126" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="E126" s="3" t="s">
+      <c r="E126" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="F126" s="3" t="n">
+      <c r="F126" s="4" t="n">
         <v>124</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="3" t="s">
+    <row r="127" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="C127" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D127" s="3" t="s">
+      <c r="D127" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="E127" s="3" t="s">
+      <c r="E127" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="F127" s="3" t="n">
+      <c r="F127" s="4" t="n">
         <v>125</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="4" t="s">
+    <row r="128" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="D128" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="E128" s="4" t="s">
+      <c r="E128" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="F128" s="4" t="n">
+      <c r="F128" s="5" t="n">
         <v>126</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="3" t="s">
+    <row r="129" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="C129" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="D129" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="E129" s="3" t="s">
+      <c r="E129" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="F129" s="3" t="n">
+      <c r="F129" s="4" t="n">
         <v>127</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="4" t="s">
+    <row r="130" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B130" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D130" s="4" t="s">
+      <c r="D130" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E130" s="4" t="s">
+      <c r="E130" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="F130" s="4" t="n">
+      <c r="F130" s="5" t="n">
         <v>128</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="3" t="s">
+    <row r="131" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C131" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D131" s="3" t="s">
+      <c r="D131" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="E131" s="3" t="s">
+      <c r="E131" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="F131" s="3" t="n">
+      <c r="F131" s="4" t="n">
         <v>129</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="4" t="s">
+    <row r="132" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D132" s="4" t="s">
+      <c r="D132" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="E132" s="4" t="s">
+      <c r="E132" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="F132" s="4" t="n">
+      <c r="F132" s="5" t="n">
         <v>130</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="4" t="s">
+    <row r="133" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B133" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D133" s="4" t="s">
+      <c r="D133" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="E133" s="4" t="s">
+      <c r="E133" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="F133" s="4" t="n">
+      <c r="F133" s="5" t="n">
         <v>131</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="4" t="s">
+    <row r="134" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D134" s="4" t="s">
+      <c r="D134" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="E134" s="4" t="s">
+      <c r="E134" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="F134" s="4" t="n">
+      <c r="F134" s="5" t="n">
         <v>132</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="4" t="s">
+    <row r="135" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D135" s="4" t="s">
+      <c r="D135" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="E135" s="4" t="s">
+      <c r="E135" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="F135" s="4" t="n">
+      <c r="F135" s="5" t="n">
         <v>133</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="3" t="s">
+    <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="C136" s="3" t="s">
+      <c r="C136" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D136" s="3" t="s">
+      <c r="D136" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="E136" s="3" t="s">
+      <c r="E136" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="F136" s="3" t="n">
+      <c r="F136" s="4" t="n">
         <v>134</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="3" t="s">
+    <row r="137" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="C137" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D137" s="3" t="s">
+      <c r="D137" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="E137" s="3" t="s">
+      <c r="E137" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="F137" s="3" t="n">
+      <c r="F137" s="4" t="n">
         <v>135</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="3" t="s">
+    <row r="138" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A138" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="C138" s="3" t="s">
+      <c r="C138" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D138" s="3" t="s">
+      <c r="D138" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="E138" s="3" t="s">
+      <c r="E138" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="F138" s="3" t="n">
+      <c r="F138" s="4" t="n">
         <v>136</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="3" t="s">
+    <row r="139" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A139" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="C139" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D139" s="3" t="s">
+      <c r="D139" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="E139" s="3" t="s">
+      <c r="E139" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="F139" s="3" t="n">
+      <c r="F139" s="4" t="n">
         <v>137</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="4" t="s">
+    <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="C140" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D140" s="4" t="s">
+      <c r="D140" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="E140" s="4" t="s">
+      <c r="E140" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="F140" s="4" t="n">
+      <c r="F140" s="5" t="n">
         <v>138</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="4" t="s">
+    <row r="141" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C141" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D141" s="4" t="s">
+      <c r="D141" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="E141" s="4" t="s">
+      <c r="E141" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="F141" s="4" t="n">
+      <c r="F141" s="5" t="n">
         <v>139</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="4" t="s">
+    <row r="142" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B142" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="C142" s="4" t="s">
+      <c r="C142" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D142" s="4" t="s">
+      <c r="D142" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="E142" s="4" t="s">
+      <c r="E142" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="F142" s="4" t="n">
+      <c r="F142" s="5" t="n">
         <v>140</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="3" t="s">
+    <row r="143" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="C143" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D143" s="3" t="s">
+      <c r="D143" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="E143" s="3" t="s">
+      <c r="E143" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="F143" s="3" t="n">
+      <c r="F143" s="4" t="n">
         <v>141</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="3" t="s">
+    <row r="144" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="C144" s="3" t="s">
+      <c r="C144" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D144" s="3" t="s">
+      <c r="D144" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="E144" s="3" t="s">
+      <c r="E144" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="F144" s="3" t="n">
+      <c r="F144" s="4" t="n">
         <v>142</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="4" t="s">
+    <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B145" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="C145" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D145" s="4" t="s">
+      <c r="D145" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="E145" s="4" t="s">
+      <c r="E145" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="F145" s="4" t="n">
+      <c r="F145" s="5" t="n">
         <v>143</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="4" t="s">
+    <row r="146" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B146" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="C146" s="4" t="s">
+      <c r="C146" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D146" s="4" t="s">
+      <c r="D146" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="E146" s="4" t="s">
+      <c r="E146" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="F146" s="4" t="n">
+      <c r="F146" s="5" t="n">
         <v>144</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="4" t="s">
+    <row r="147" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B147" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="C147" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D147" s="4" t="s">
+      <c r="D147" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="E147" s="4" t="s">
+      <c r="E147" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="F147" s="4" t="n">
+      <c r="F147" s="5" t="n">
         <v>145</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="4" t="s">
+    <row r="148" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="B148" s="4" t="s">
+      <c r="B148" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="C148" s="4" t="s">
+      <c r="C148" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D148" s="4" t="s">
+      <c r="D148" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="E148" s="4" t="s">
+      <c r="E148" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="F148" s="4" t="n">
+      <c r="F148" s="5" t="n">
         <v>146</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="3" t="s">
+    <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="C149" s="3" t="s">
+      <c r="C149" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D149" s="3" t="s">
+      <c r="D149" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="E149" s="3" t="s">
+      <c r="E149" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="F149" s="3" t="n">
+      <c r="F149" s="4" t="n">
         <v>147</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="3" t="s">
+    <row r="150" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B150" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="C150" s="3" t="s">
+      <c r="C150" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D150" s="3" t="s">
+      <c r="D150" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="E150" s="3" t="s">
+      <c r="E150" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="F150" s="3" t="n">
+      <c r="F150" s="4" t="n">
         <v>148</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="4" t="s">
+    <row r="151" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="C151" s="4" t="s">
+      <c r="C151" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D151" s="4" t="s">
+      <c r="D151" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="E151" s="4" t="s">
+      <c r="E151" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="F151" s="4" t="n">
+      <c r="F151" s="5" t="n">
         <v>149</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="4" t="s">
+    <row r="152" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B152" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="C152" s="4" t="s">
+      <c r="C152" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D152" s="4" t="s">
+      <c r="D152" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="E152" s="4" t="s">
+      <c r="E152" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="F152" s="4" t="n">
+      <c r="F152" s="5" t="n">
         <v>150</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="3" t="s">
+    <row r="153" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B153" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="C153" s="3" t="s">
+      <c r="C153" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D153" s="3" t="s">
+      <c r="D153" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="E153" s="3" t="s">
+      <c r="E153" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="F153" s="3" t="n">
+      <c r="F153" s="4" t="n">
         <v>151</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="3" t="s">
+    <row r="154" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B154" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="C154" s="3" t="s">
+      <c r="C154" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D154" s="3" t="s">
+      <c r="D154" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="E154" s="3" t="s">
+      <c r="E154" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="F154" s="3" t="n">
+      <c r="F154" s="4" t="n">
         <v>152</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="4" t="s">
+    <row r="155" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B155" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="C155" s="4" t="s">
+      <c r="C155" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D155" s="4" t="s">
+      <c r="D155" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="E155" s="4" t="s">
+      <c r="E155" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="F155" s="4" t="n">
+      <c r="F155" s="5" t="n">
         <v>153</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="4" t="s">
+    <row r="156" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="B156" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="C156" s="4" t="s">
+      <c r="C156" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D156" s="4" t="s">
+      <c r="D156" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="E156" s="4" t="s">
+      <c r="E156" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="F156" s="4" t="n">
+      <c r="F156" s="5" t="n">
         <v>154</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="3" t="s">
+    <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B157" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C157" s="3" t="s">
+      <c r="C157" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D157" s="3" t="s">
+      <c r="D157" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="E157" s="3" t="s">
+      <c r="E157" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="F157" s="3" t="n">
+      <c r="F157" s="4" t="n">
         <v>155</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="3" t="s">
+    <row r="158" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B158" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="C158" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D158" s="3" t="s">
+      <c r="D158" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="E158" s="3" t="s">
+      <c r="E158" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="F158" s="3" t="n">
+      <c r="F158" s="4" t="n">
         <v>156</v>
       </c>
     </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C159" s="4"/>
+      <c r="D159" s="4"/>
+      <c r="E159" s="4"/>
+      <c r="F159" s="4" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C160" s="4"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="4"/>
+      <c r="F160" s="4" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C161" s="4"/>
+      <c r="D161" s="4"/>
+      <c r="E161" s="4"/>
+      <c r="F161" s="4" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C162" s="4"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="4" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C163" s="4"/>
+      <c r="D163" s="4"/>
+      <c r="E163" s="4"/>
+      <c r="F163" s="4" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C164" s="4"/>
+      <c r="D164" s="4"/>
+      <c r="E164" s="4"/>
+      <c r="F164" s="4" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C165" s="4"/>
+      <c r="D165" s="4"/>
+      <c r="E165" s="4"/>
+      <c r="F165" s="4" t="n">
+        <v>163</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F158"/>
+  <autoFilter ref="A2:F165"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -6656,2531 +6815,2650 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A1" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="D2" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>527</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="C3" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="C6" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="B7" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>541</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="B8" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>543</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="C9" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="C10" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="C11" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="C12" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
+      <c r="C13" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
+      <c r="C14" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
+      <c r="C15" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+      <c r="C16" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
+      <c r="C17" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+      <c r="C18" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
+      <c r="C19" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
+      <c r="C20" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
+      <c r="C21" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
+      <c r="C22" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
+      <c r="C23" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
+      <c r="C24" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
+      <c r="C25" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="C26" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
+      <c r="C27" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
+      <c r="C28" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
+      <c r="C29" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
+      <c r="C30" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="n">
+      <c r="C31" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="n">
+      <c r="B32" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="n">
+      <c r="C33" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
+      <c r="B34" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="n">
+      <c r="C35" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
+      <c r="C36" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="n">
+      <c r="C37" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
+      <c r="B38" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="n">
+      <c r="C39" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="n">
+      <c r="C40" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4" t="s">
+      <c r="B41" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>683</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>705</v>
+      </c>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>790</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>638</v>
-      </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>643</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>644</v>
-      </c>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>650</v>
-      </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>655</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>656</v>
-      </c>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>659</v>
-      </c>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>664</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>676</v>
-      </c>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>679</v>
-      </c>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>699</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>700</v>
-      </c>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>702</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>703</v>
-      </c>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>706</v>
-      </c>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>709</v>
-      </c>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>711</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>714</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>717</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>723</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>726</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>727</v>
-      </c>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>729</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>730</v>
-      </c>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>732</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>735</v>
-      </c>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>740</v>
-      </c>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>742</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>743</v>
-      </c>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>745</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>750</v>
-      </c>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>752</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>756</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>757</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>760</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>761</v>
-      </c>
-      <c r="D84" s="5" t="s">
+      <c r="C95" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>802</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>806</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="E84" s="4" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>763</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>764</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>765</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>766</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>767</v>
-      </c>
-      <c r="D86" s="5" t="s">
+      <c r="C98" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>819</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>821</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>824</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>826</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>829</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>832</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>832</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="E86" s="4" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>770</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>772</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>775</v>
-      </c>
-      <c r="D88" s="5" t="s">
+      <c r="C113" s="5" t="s">
+        <v>854</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="5" t="s">
         <v>776</v>
       </c>
-      <c r="E88" s="4" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>777</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>778</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>779</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>780</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>781</v>
-      </c>
-      <c r="D90" s="5" t="s">
+      <c r="C114" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="5" t="s">
         <v>782</v>
       </c>
-      <c r="E90" s="4" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>784</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>785</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>786</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>787</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>788</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>790</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>791</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>792</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>793</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>794</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>795</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>797</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>798</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>780</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>800</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>801</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>802</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>803</v>
-      </c>
-      <c r="D97" s="5" t="s">
+      <c r="C116" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>864</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>876</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>880</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>882</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>886</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>890</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>896</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>900</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>916</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>920</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>922</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>924</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>926</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>930</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A138" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>931</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>932</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A139" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>935</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="E97" s="4" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>760</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>805</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>806</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>807</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>808</v>
-      </c>
-      <c r="D99" s="5" t="s">
+      <c r="C140" s="5" t="s">
+        <v>939</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="E99" s="4" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>811</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>780</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>814</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>815</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>817</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>818</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>819</v>
-      </c>
-      <c r="E102" s="4" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>760</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>822</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>824</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>825</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>826</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>827</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>828</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>830</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>831</v>
-      </c>
-      <c r="D106" s="5" t="s">
+      <c r="C141" s="5" t="s">
+        <v>941</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>942</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>945</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>948</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>950</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>951</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>954</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>956</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>957</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>960</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>964</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>965</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>968</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>900</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>970</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>971</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>972</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>971</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>975</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>977</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>978</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>980</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>978</v>
+      </c>
+      <c r="E154" s="5" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>981</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>982</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>983</v>
+      </c>
+      <c r="E155" s="5" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>985</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>986</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>988</v>
+      </c>
+      <c r="D157" s="5"/>
+      <c r="E157" s="5" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>990</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>991</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>992</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>994</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>996</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>997</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>832</v>
       </c>
-      <c r="E106" s="4" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>834</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>835</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>836</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>830</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>838</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>839</v>
-      </c>
-      <c r="E108" s="4" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>841</v>
-      </c>
-      <c r="C109" s="4" t="s">
-        <v>842</v>
-      </c>
-      <c r="D109" s="5" t="s">
+      <c r="C161" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>999</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" s="5" t="s">
         <v>843</v>
       </c>
-      <c r="E109" s="4" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="4" t="n">
-        <v>108</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="4" t="n">
-        <v>109</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>834</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>847</v>
-      </c>
-      <c r="E111" s="4" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>849</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>850</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>766</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>852</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>853</v>
-      </c>
-      <c r="E113" s="4" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>854</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>855</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>857</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>858</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>859</v>
-      </c>
-      <c r="E115" s="4" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>780</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>861</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>862</v>
-      </c>
-      <c r="E116" s="4" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>863</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>864</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>865</v>
-      </c>
-      <c r="E117" s="4" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>780</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>867</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>868</v>
-      </c>
-      <c r="E118" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="4" t="n">
-        <v>117</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>869</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>870</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>871</v>
-      </c>
-      <c r="E119" s="4" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>857</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>873</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>874</v>
-      </c>
-      <c r="E120" s="4" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>876</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>877</v>
-      </c>
-      <c r="D121" s="5" t="s">
-        <v>878</v>
-      </c>
-      <c r="E121" s="4" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>879</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>880</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>881</v>
-      </c>
-      <c r="E122" s="4" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="4" t="n">
-        <v>121</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>780</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>883</v>
-      </c>
-      <c r="D123" s="5" t="s">
-        <v>884</v>
-      </c>
-      <c r="E123" s="4" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="4" t="n">
-        <v>122</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>841</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>885</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>886</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="4" t="n">
-        <v>123</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>807</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>887</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>888</v>
-      </c>
-      <c r="E125" s="4" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="4" t="n">
-        <v>124</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>890</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>891</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>892</v>
-      </c>
-      <c r="E126" s="4" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>826</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>893</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>894</v>
-      </c>
-      <c r="E127" s="4" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="4" t="n">
-        <v>126</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>896</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>897</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>898</v>
-      </c>
-      <c r="E128" s="4" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="4" t="n">
-        <v>127</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>900</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>901</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>902</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>904</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>905</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>902</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>907</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>908</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>902</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>909</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>910</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>911</v>
-      </c>
-      <c r="E132" s="4" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="4" t="n">
-        <v>131</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>914</v>
-      </c>
-      <c r="D133" s="5" t="s">
-        <v>915</v>
-      </c>
-      <c r="E133" s="4" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>917</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>918</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="4" t="n">
-        <v>133</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>920</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>921</v>
-      </c>
-      <c r="D135" s="5" t="s">
-        <v>922</v>
-      </c>
-      <c r="E135" s="4" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="4" t="n">
-        <v>134</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>924</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>925</v>
-      </c>
-      <c r="E136" s="4" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="4" t="n">
-        <v>135</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>926</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>927</v>
-      </c>
-      <c r="D137" s="5" t="s">
-        <v>928</v>
-      </c>
-      <c r="E137" s="4" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="4" t="n">
-        <v>136</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>929</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>930</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>931</v>
-      </c>
-      <c r="E138" s="4" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="4" t="n">
-        <v>137</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>933</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>934</v>
-      </c>
-      <c r="D139" s="5" t="s">
-        <v>935</v>
-      </c>
-      <c r="E139" s="4" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="4" t="n">
-        <v>138</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>802</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>937</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>938</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="4" t="n">
-        <v>139</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>807</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>939</v>
-      </c>
-      <c r="D141" s="5" t="s">
-        <v>940</v>
-      </c>
-      <c r="E141" s="4" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>942</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>943</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>944</v>
-      </c>
-      <c r="E142" s="4" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="4" t="n">
-        <v>141</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="D143" s="5" t="s">
-        <v>947</v>
-      </c>
-      <c r="E143" s="4" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="4" t="n">
-        <v>142</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>948</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>949</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>950</v>
-      </c>
-      <c r="E144" s="4" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="4" t="n">
-        <v>143</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>834</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>952</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>953</v>
-      </c>
-      <c r="E145" s="4" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="4" t="n">
-        <v>144</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>954</v>
-      </c>
-      <c r="D146" s="5" t="s">
-        <v>955</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>957</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>958</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>959</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="4" t="n">
-        <v>146</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>961</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>962</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>963</v>
-      </c>
-      <c r="E148" s="4" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="4" t="n">
-        <v>147</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>965</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>966</v>
-      </c>
-      <c r="D149" s="5" t="s">
-        <v>898</v>
-      </c>
-      <c r="E149" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="4" t="n">
-        <v>148</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>967</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>968</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>902</v>
-      </c>
-      <c r="E150" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>969</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>970</v>
-      </c>
-      <c r="D151" s="5" t="s">
-        <v>971</v>
-      </c>
-      <c r="E151" s="4" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>969</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>973</v>
-      </c>
-      <c r="D152" s="5" t="s">
-        <v>971</v>
-      </c>
-      <c r="E152" s="4" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="4" t="n">
-        <v>151</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>974</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>975</v>
-      </c>
-      <c r="D153" s="5" t="s">
-        <v>976</v>
-      </c>
-      <c r="E153" s="4" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="4" t="n">
-        <v>152</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>974</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>978</v>
-      </c>
-      <c r="D154" s="5" t="s">
-        <v>976</v>
-      </c>
-      <c r="E154" s="4" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="4" t="n">
-        <v>153</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>979</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>980</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>981</v>
-      </c>
-      <c r="E155" s="4" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="4" t="n">
-        <v>154</v>
-      </c>
-      <c r="B156" s="4" t="s">
-        <v>807</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>983</v>
-      </c>
-      <c r="D156" s="5" t="s">
-        <v>984</v>
-      </c>
-      <c r="E156" s="4" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="4" t="n">
-        <v>155</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>985</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>986</v>
-      </c>
-      <c r="D157" s="4"/>
-      <c r="E157" s="4" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>988</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>989</v>
-      </c>
-      <c r="D158" s="5" t="s">
-        <v>990</v>
-      </c>
-      <c r="E158" s="4" t="s">
-        <v>987</v>
+      <c r="C164" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E164" s="5" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E165" s="5" t="s">
+        <v>1007</v>
       </c>
     </row>
   </sheetData>
@@ -9264,6 +9542,13 @@
     <hyperlink ref="D155" r:id="rId74" display="https://www.npr.org/2026/06/30/nx-s1-5839358/birthright-citizenship-decision-scotus-trump"/>
     <hyperlink ref="D156" r:id="rId75" display="https://www.cnn.com/2026/06/30/politics/live-news/supreme-court-cases-news"/>
     <hyperlink ref="D158" r:id="rId76" display="https://www.bostonglobe.com/2026/07/07/nation/trump-presidency-live-updates/"/>
+    <hyperlink ref="D159" r:id="rId77" display="https://www.nbcnews.com/politics/donald-trump/palm-beach-international-airport-tennessee-bridge-renamed-rcna353784"/>
+    <hyperlink ref="D160" r:id="rId78" display="https://www.theguardian.com/politics/video/2026/jul/10/trump-restarts-war-with-iran-and-plays-niceish-with-nato-politics-weekly-america"/>
+    <hyperlink ref="D161" r:id="rId79" display="https://abcnews.com/Politics/wireStory/crews-draining-lincoln-memorial-reflecting-pool-part-trumps-134656303"/>
+    <hyperlink ref="D162" r:id="rId80" display="https://www.pbs.org/newshour/show/trump-fires-election-commission-members-in-latest-attempt-to-control-voting-process"/>
+    <hyperlink ref="D163" r:id="rId81" display="https://www.pbs.org/newshour/politics/federal-officials-refusing-to-release-name-of-ice-officer-who-fatally-shot-lorenzo-salgado-araujo"/>
+    <hyperlink ref="D164" r:id="rId82" display="https://www.npr.org/2026/07/11/g-s1-133160/justice-department-subpoenas-new-york-times-reporters-over-air-force-one-reporting"/>
+    <hyperlink ref="D165" r:id="rId83" display="https://www.nbcnews.com/politics/justice-department/judge-grants-doj-request-toss-remaining-jan-6-convictions-proud-boys-rcna385952"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9283,182 +9568,182 @@
   <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>991</v>
-      </c>
-      <c r="B1" s="6"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B1" s="7"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="B2" s="8" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B3" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A3)</f>
+      <c r="B3" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A3)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A4)</f>
+      <c r="B4" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A4)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="B5" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A5)</f>
+      <c r="B5" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A5)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A6)</f>
+      <c r="B6" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A6)</f>
         <v>34</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A7)</f>
+      <c r="B7" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A7)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A8)</f>
+      <c r="B8" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A8)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A9)</f>
+      <c r="B9" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A9)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A10)</f>
+      <c r="B10" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A10)</f>
         <v>27</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A11)</f>
+      <c r="B11" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A11)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A12)</f>
+      <c r="B12" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A12)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B13" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A13)</f>
+      <c r="B13" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A13)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A14)</f>
+      <c r="B14" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A14)</f>
         <v>19</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B15" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A15)</f>
+      <c r="B15" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A15)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A16)</f>
+      <c r="B16" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A16)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A17)</f>
+      <c r="B17" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A17)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A18)</f>
+      <c r="B18" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A18)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="B19" s="8" t="n">
-        <f aca="false">COUNTIF('Weekly Timeline'!$C$3:$C$158,A19)</f>
+      <c r="B19" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A19)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
-        <v>993</v>
-      </c>
-      <c r="B20" s="9" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B20" s="10" t="n">
         <f aca="false">SUM(B3:B19)</f>
         <v>156</v>
       </c>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -6696,7 +6696,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="4" t="s">
         <v>516</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="4" t="s">
         <v>516</v>
       </c>
@@ -6724,7 +6724,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="4" t="s">
         <v>516</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="4" t="s">
         <v>516</v>
       </c>
@@ -6752,7 +6752,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="4" t="s">
         <v>516</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="4" t="s">
         <v>516</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="4" t="s">
         <v>516</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="5" t="n">
         <v>157</v>
       </c>
@@ -9359,7 +9359,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="5" t="n">
         <v>158</v>
       </c>
@@ -9376,7 +9376,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="5" t="n">
         <v>159</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="5" t="n">
         <v>160</v>
       </c>
@@ -9410,7 +9410,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="5" t="n">
         <v>161</v>
       </c>
@@ -9427,7 +9427,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="5" t="n">
         <v>162</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="5" t="n">
         <v>163</v>
       </c>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Timeline" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Sources" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Weekly Timeline" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sources" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$165</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$158</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -3255,6 +3255,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF1F3864"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3262,13 +3263,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9E2F3"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3276,6 +3278,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3347,8 +3350,183 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1f497d"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="eeece1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4f81bd"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="c0504d"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9bbb59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064a2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4bacc6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="f79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ff"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -6569,7 +6747,7 @@
       <c r="F165" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F165"/>
+  <autoFilter ref="A2:F158"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -6585,7 +6763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -9335,7 +9513,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$158</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$160</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="1019">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1590,6 +1590,15 @@
     <t xml:space="preserve">Nearly 11 months of military presence in Washington with no end date</t>
   </si>
   <si>
+    <t xml:space="preserve">Jul 13, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3049,6 +3058,21 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.nbcnews.com/politics/justice-department/judge-grants-doj-request-toss-remaining-jan-6-convictions-proud-boys-rcna385952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICE shot and killed a Colombian man in Maine. This is the 2nd time in a week the agency used deadly force</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/nation/ice-shot-and-killed-a-colombian-man-in-maine-this-is-the-2nd-time-in-a-week-the-agency-used-deadly-force</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Military action against Iran formally restarted last week, Trump told lawmakers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cbsnews.com/news/iran-military-action-formally-restarted-trump-lawmakers-war-powers/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 14, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -6691,20 +6715,32 @@
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="4"/>
-      <c r="B159" s="4"/>
+      <c r="A159" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>522</v>
+      </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
-      <c r="F159" s="4"/>
+      <c r="F159" s="4" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="4"/>
-      <c r="B160" s="4"/>
+      <c r="A160" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>523</v>
+      </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
-      <c r="F160" s="4"/>
+      <c r="F160" s="4" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="4"/>
@@ -6747,7 +6783,7 @@
       <c r="F165" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F158"/>
+  <autoFilter ref="A2:F160"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -6767,7 +6803,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -6778,7 +6814,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6787,19 +6823,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6807,14 +6843,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6822,14 +6858,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6837,14 +6873,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6852,14 +6888,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6867,14 +6903,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6882,14 +6918,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6897,14 +6933,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6912,14 +6948,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6927,14 +6963,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6942,14 +6978,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6957,14 +6993,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6972,14 +7008,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6987,14 +7023,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7002,14 +7038,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7017,14 +7053,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7032,14 +7068,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7047,14 +7083,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7062,14 +7098,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7077,14 +7113,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7092,14 +7128,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7107,14 +7143,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7122,14 +7158,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7137,14 +7173,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7152,14 +7188,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7167,14 +7203,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7182,14 +7218,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7197,14 +7233,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7212,14 +7248,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7227,14 +7263,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7242,14 +7278,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7257,14 +7293,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7272,14 +7308,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7287,14 +7323,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7302,14 +7338,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7317,14 +7353,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7332,14 +7368,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7347,14 +7383,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7362,14 +7398,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7377,10 +7413,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -7392,14 +7428,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7407,14 +7443,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7422,14 +7458,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7437,14 +7473,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7452,14 +7488,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7467,14 +7503,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7482,14 +7518,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7497,14 +7533,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7512,14 +7548,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7527,14 +7563,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7542,14 +7578,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7557,14 +7593,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7572,14 +7608,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7587,14 +7623,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7602,14 +7638,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7617,14 +7653,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7632,14 +7668,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7647,14 +7683,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7662,14 +7698,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7677,14 +7713,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7692,14 +7728,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7707,14 +7743,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7722,14 +7758,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7737,14 +7773,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7752,14 +7788,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7767,14 +7803,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7782,14 +7818,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7797,14 +7833,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7812,14 +7848,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7827,14 +7863,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7842,14 +7878,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7857,14 +7893,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7872,14 +7908,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7887,14 +7923,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7902,14 +7938,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7917,14 +7953,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7932,14 +7968,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7947,14 +7983,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7962,14 +7998,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7977,14 +8013,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7992,16 +8028,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8009,16 +8045,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8026,13 +8062,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -8043,13 +8079,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -8060,16 +8096,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8077,16 +8113,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8094,16 +8130,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="D88" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>776</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8111,16 +8147,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8128,16 +8164,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8145,16 +8181,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="D91" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8162,16 +8198,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8179,16 +8215,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="D93" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>792</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8196,16 +8232,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8213,16 +8249,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8230,16 +8266,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8247,16 +8283,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>802</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>803</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>804</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8264,16 +8300,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8281,16 +8317,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8298,16 +8334,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8315,16 +8351,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8332,16 +8368,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8349,16 +8385,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8366,13 +8402,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -8383,16 +8419,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8400,16 +8436,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8417,16 +8453,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8434,16 +8470,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8451,13 +8487,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -8468,13 +8504,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -8485,16 +8521,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8502,16 +8538,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8519,13 +8555,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -8536,16 +8572,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8553,16 +8589,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8570,16 +8606,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8587,16 +8623,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8604,13 +8640,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -8621,16 +8657,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8638,16 +8674,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8655,16 +8691,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8672,16 +8708,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8689,13 +8725,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -8706,13 +8742,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -8723,16 +8759,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8740,16 +8776,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="D126" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="E126" s="5" t="s">
         <v>892</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8757,16 +8793,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8774,16 +8810,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8791,16 +8827,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8808,16 +8844,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="C130" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="D130" s="6" t="s">
         <v>905</v>
       </c>
-      <c r="D130" s="6" t="s">
-        <v>902</v>
-      </c>
       <c r="E130" s="5" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8825,13 +8861,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -8842,16 +8878,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8859,16 +8895,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="D133" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="E133" s="5" t="s">
         <v>915</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8876,16 +8912,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8893,16 +8929,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8910,13 +8946,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -8927,13 +8963,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -8944,16 +8980,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8961,16 +8997,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8978,13 +9014,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -8995,16 +9031,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9012,16 +9048,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9029,13 +9065,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -9046,16 +9082,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9063,13 +9099,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -9080,16 +9116,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9097,16 +9133,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9114,16 +9150,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9131,13 +9167,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -9148,13 +9184,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -9165,16 +9201,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9182,16 +9218,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9199,16 +9235,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9216,16 +9252,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9233,16 +9269,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9250,16 +9286,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9267,14 +9303,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9282,16 +9318,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="D158" s="6" t="s">
+        <v>993</v>
+      </c>
+      <c r="E158" s="5" t="s">
         <v>990</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9299,16 +9335,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9316,16 +9352,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9333,16 +9369,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C161" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>996</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>997</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9350,16 +9386,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9367,16 +9403,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9384,16 +9420,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9401,16 +9437,50 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1005</v>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>1015</v>
       </c>
     </row>
   </sheetData>
@@ -9501,6 +9571,8 @@
     <hyperlink ref="D163" r:id="rId81" display="https://www.pbs.org/newshour/politics/federal-officials-refusing-to-release-name-of-ice-officer-who-fatally-shot-lorenzo-salgado-araujo"/>
     <hyperlink ref="D164" r:id="rId82" display="https://www.npr.org/2026/07/11/g-s1-133160/justice-department-subpoenas-new-york-times-reporters-over-air-force-one-reporting"/>
     <hyperlink ref="D165" r:id="rId83" display="https://www.nbcnews.com/politics/justice-department/judge-grants-doj-request-toss-remaining-jan-6-convictions-proud-boys-rcna385952"/>
+    <hyperlink ref="D166" r:id="rId84" display="https://www.pbs.org/newshour/nation/ice-shot-and-killed-a-colombian-man-in-maine-this-is-the-2nd-time-in-a-week-the-agency-used-deadly-force"/>
+    <hyperlink ref="D167" r:id="rId85" display="https://www.cbsnews.com/news/iran-military-action-formally-restarted-trump-lawmakers-war-powers/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9526,7 +9598,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -9535,7 +9607,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9693,7 +9765,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="B20" s="10" t="n">
         <f aca="false">SUM(B3:B19)</f>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$160</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$173</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="1019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="1055">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1599,6 +1599,24 @@
     <t xml:space="preserve">Jul 14</t>
   </si>
   <si>
+    <t xml:space="preserve">Aug 17, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 21</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3073,6 +3091,96 @@
   </si>
   <si>
     <t xml:space="preserve">Jul 14, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump ‘doesn’t have a plan’ on Iran: Voters in key Pennsylvania district upset with handling of war</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/meet-the-press/video/trump-doesn-t-have-a-plan-on-iran-voters-in-key-pennsylvania-district-upset-with-handling-of-war-268422725765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Congresswoman says target of ICE operation in fatal Maine shooting wasn't up for removal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/congresswoman-target-ice-operation-fatal-maine-shooting-removal-135749324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 18, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump administration moves ahead to end roadless rule on national forests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/trump-administration-moves-ahead-end-roadless-rule-national-135748769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senator presses Hegseth, Caine for commitment to keep US military out of the midterm elections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/senator-presses-hegseth-caine-commitment-us-military-midterm-135745047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump tries to quiet his mass deportation campaign. Voters aren’t moving.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.politico.com/news/2026/08/19/poll-trump-deportations-voters-midterms-01041099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 19, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Has Trump no shame about all the money he has made since being in office? | Francine Prose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/commentisfree/2026/aug/20/trump-money-earnings-billionaires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 20, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From ‘predator’ to ‘conman’: how Michael Cohen has described Trump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/2026/aug/20/michael-cohen-donald-trump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump talks about grass as he shows off White House renovations – video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/video/2026/aug/19/trump-talks-grass-white-house</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supreme Court allows Trump's ballroom construction to continue for now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.npr.org/2026/08/21/nx-s1-5935417/supreme-court-allows-trumps-ballroom-construction-to-continue-for-now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 21, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karoline Leavitt to work for Trump-affiliated super PAC after leaving White House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/white-house/karoline-leavitt-work-trump-affiliated-super-pac-leaving-white-house-rcna593824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navy discusses renaming aircraft carrier after Trump instead of heroic Black sailor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/trump-administration/navy-discusses-renaming-aircraft-carrier-trump-black-uss-doris-miller-rcna593667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pentagon moves to fire publisher and editor of Stars and Stripes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cbsnews.com/news/stars-and-stripes-publisher-editor-separation-notices-pentagon/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Court says prosecutor who subpoenaed Letitia James was unlawfully appointed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cbsnews.com/news/appeals-court-john-sarcone-letitia-james-federal-prosecutor/</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -3554,7 +3662,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F165"/>
+  <dimension ref="A1:F173"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -6743,47 +6851,189 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="4"/>
-      <c r="B161" s="4"/>
+      <c r="A161" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>525</v>
+      </c>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
-      <c r="F161" s="4"/>
+      <c r="F161" s="4" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="4"/>
-      <c r="B162" s="4"/>
+      <c r="A162" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>526</v>
+      </c>
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
-      <c r="F162" s="4"/>
+      <c r="F162" s="4" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="4"/>
-      <c r="B163" s="4"/>
+      <c r="A163" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>526</v>
+      </c>
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
-      <c r="F163" s="4"/>
+      <c r="F163" s="4" t="n">
+        <v>161</v>
+      </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="4"/>
-      <c r="B164" s="4"/>
+      <c r="A164" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>526</v>
+      </c>
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
-      <c r="F164" s="4"/>
+      <c r="F164" s="4" t="n">
+        <v>162</v>
+      </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="4"/>
-      <c r="B165" s="4"/>
+      <c r="A165" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>527</v>
+      </c>
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
-      <c r="F165" s="4"/>
+      <c r="F165" s="4" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="C166" s="5"/>
+      <c r="D166" s="5"/>
+      <c r="E166" s="5"/>
+      <c r="F166" s="5" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="C167" s="5"/>
+      <c r="D167" s="5"/>
+      <c r="E167" s="5"/>
+      <c r="F167" s="5" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="C168" s="5"/>
+      <c r="D168" s="5"/>
+      <c r="E168" s="5"/>
+      <c r="F168" s="5" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C169" s="5"/>
+      <c r="D169" s="5"/>
+      <c r="E169" s="5"/>
+      <c r="F169" s="5" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C170" s="5"/>
+      <c r="D170" s="5"/>
+      <c r="E170" s="5"/>
+      <c r="F170" s="5" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C171" s="5"/>
+      <c r="D171" s="5"/>
+      <c r="E171" s="5"/>
+      <c r="F171" s="5" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C172" s="5"/>
+      <c r="D172" s="5"/>
+      <c r="E172" s="5"/>
+      <c r="F172" s="5" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C173" s="5"/>
+      <c r="D173" s="5"/>
+      <c r="E173" s="5"/>
+      <c r="F173" s="5" t="n">
+        <v>171</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F160"/>
+  <autoFilter ref="A2:F173"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -6803,7 +7053,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E167"/>
+  <dimension ref="A1:E180"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -6814,7 +7064,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6823,19 +7073,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6843,14 +7093,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6858,14 +7108,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6873,14 +7123,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6888,14 +7138,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6903,14 +7153,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6918,14 +7168,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6933,14 +7183,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6948,14 +7198,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6963,14 +7213,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6978,14 +7228,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6993,14 +7243,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7008,14 +7258,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7023,14 +7273,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7038,14 +7288,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7053,14 +7303,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7068,14 +7318,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7083,14 +7333,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7098,14 +7348,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7113,14 +7363,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7128,14 +7378,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7143,14 +7393,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7158,14 +7408,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7173,14 +7423,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7188,14 +7438,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7203,14 +7453,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7218,14 +7468,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7233,14 +7483,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7248,14 +7498,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7263,14 +7513,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7278,14 +7528,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7293,14 +7543,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7308,14 +7558,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7323,14 +7573,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7338,14 +7588,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7353,14 +7603,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7368,14 +7618,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7383,14 +7633,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7398,14 +7648,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7413,10 +7663,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -7428,14 +7678,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7443,14 +7693,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7458,14 +7708,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7473,14 +7723,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7488,14 +7738,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7503,14 +7753,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7518,14 +7768,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7533,14 +7783,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7548,14 +7798,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7563,14 +7813,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7578,14 +7828,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7593,14 +7843,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7608,14 +7858,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7623,14 +7873,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7638,14 +7888,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7653,14 +7903,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7668,14 +7918,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7683,14 +7933,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7698,14 +7948,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7713,14 +7963,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7728,14 +7978,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7743,14 +7993,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7758,14 +8008,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7773,14 +8023,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7788,14 +8038,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7803,14 +8053,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7818,14 +8068,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7833,14 +8083,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7848,14 +8098,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7863,14 +8113,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7878,14 +8128,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7893,14 +8143,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7908,14 +8158,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7923,14 +8173,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7938,14 +8188,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7953,14 +8203,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7968,14 +8218,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7983,14 +8233,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7998,14 +8248,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8013,14 +8263,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8028,16 +8278,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8045,16 +8295,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8062,13 +8312,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -8079,13 +8329,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -8096,16 +8346,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8113,16 +8363,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8130,16 +8380,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8147,16 +8397,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="D89" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>782</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8164,16 +8414,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8181,16 +8431,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8198,16 +8448,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8215,16 +8465,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8232,16 +8482,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8249,16 +8499,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8266,16 +8516,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8283,16 +8533,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8300,16 +8550,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8317,16 +8567,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8334,16 +8584,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8351,16 +8601,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8368,16 +8618,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8385,16 +8635,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8402,13 +8652,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -8419,16 +8669,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8436,16 +8686,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8453,16 +8703,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8470,16 +8720,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8487,13 +8737,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -8504,13 +8754,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -8521,16 +8771,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8538,16 +8788,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8555,13 +8805,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -8572,16 +8822,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8589,16 +8839,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8606,16 +8856,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8623,16 +8873,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8640,13 +8890,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -8657,16 +8907,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8674,16 +8924,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8691,16 +8941,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="D121" s="6" t="s">
+        <v>887</v>
+      </c>
+      <c r="E121" s="5" t="s">
         <v>881</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8708,16 +8958,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8725,13 +8975,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -8742,13 +8992,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -8759,16 +9009,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8776,16 +9026,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8793,16 +9043,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8810,16 +9060,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8827,16 +9077,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8844,16 +9094,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8861,13 +9111,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="C131" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="D131" s="6" t="s">
         <v>911</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>905</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -8878,16 +9128,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8895,16 +9145,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8912,16 +9162,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8929,16 +9179,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8946,13 +9196,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -8963,13 +9213,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -8980,16 +9230,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8997,16 +9247,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9014,13 +9264,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -9031,16 +9281,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9048,16 +9298,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9065,13 +9315,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -9082,16 +9332,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9099,13 +9349,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -9116,16 +9366,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9133,16 +9383,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9150,16 +9400,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9167,13 +9417,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -9184,13 +9434,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -9201,16 +9451,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9218,16 +9468,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9235,16 +9485,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9252,16 +9502,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9269,16 +9519,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9286,16 +9536,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9303,14 +9553,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9318,16 +9568,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9335,16 +9585,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9352,16 +9602,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9369,16 +9619,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9386,16 +9636,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="C162" s="5" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E162" s="5" t="s">
         <v>1002</v>
-      </c>
-      <c r="D162" s="6" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E162" s="5" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9403,16 +9653,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9420,16 +9670,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9437,50 +9687,271 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="5" t="n">
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="5" t="n">
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1015</v>
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E175" s="5" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="5" t="n">
+        <v>169</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E178" s="5" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E179" s="5" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E180" s="5" t="s">
+        <v>1043</v>
       </c>
     </row>
   </sheetData>
@@ -9573,6 +10044,19 @@
     <hyperlink ref="D165" r:id="rId83" display="https://www.nbcnews.com/politics/justice-department/judge-grants-doj-request-toss-remaining-jan-6-convictions-proud-boys-rcna385952"/>
     <hyperlink ref="D166" r:id="rId84" display="https://www.pbs.org/newshour/nation/ice-shot-and-killed-a-colombian-man-in-maine-this-is-the-2nd-time-in-a-week-the-agency-used-deadly-force"/>
     <hyperlink ref="D167" r:id="rId85" display="https://www.cbsnews.com/news/iran-military-action-formally-restarted-trump-lawmakers-war-powers/"/>
+    <hyperlink ref="D168" r:id="rId86" display="https://www.nbcnews.com/meet-the-press/video/trump-doesn-t-have-a-plan-on-iran-voters-in-key-pennsylvania-district-upset-with-handling-of-war-268422725765"/>
+    <hyperlink ref="D169" r:id="rId87" display="https://abcnews.com/Politics/wireStory/congresswoman-target-ice-operation-fatal-maine-shooting-removal-135749324"/>
+    <hyperlink ref="D170" r:id="rId88" display="https://abcnews.com/Politics/wireStory/trump-administration-moves-ahead-end-roadless-rule-national-135748769"/>
+    <hyperlink ref="D171" r:id="rId89" display="https://abcnews.com/Politics/wireStory/senator-presses-hegseth-caine-commitment-us-military-midterm-135745047"/>
+    <hyperlink ref="D172" r:id="rId90" display="https://www.politico.com/news/2026/08/19/poll-trump-deportations-voters-midterms-01041099"/>
+    <hyperlink ref="D173" r:id="rId91" display="https://www.theguardian.com/commentisfree/2026/aug/20/trump-money-earnings-billionaires"/>
+    <hyperlink ref="D174" r:id="rId92" display="https://www.theguardian.com/us-news/2026/aug/20/michael-cohen-donald-trump"/>
+    <hyperlink ref="D175" r:id="rId93" display="https://www.theguardian.com/us-news/video/2026/aug/19/trump-talks-grass-white-house"/>
+    <hyperlink ref="D176" r:id="rId94" display="https://www.npr.org/2026/08/21/nx-s1-5935417/supreme-court-allows-trumps-ballroom-construction-to-continue-for-now"/>
+    <hyperlink ref="D177" r:id="rId95" display="https://www.nbcnews.com/politics/white-house/karoline-leavitt-work-trump-affiliated-super-pac-leaving-white-house-rcna593824"/>
+    <hyperlink ref="D178" r:id="rId96" display="https://www.nbcnews.com/politics/trump-administration/navy-discusses-renaming-aircraft-carrier-trump-black-uss-doris-miller-rcna593667"/>
+    <hyperlink ref="D179" r:id="rId97" display="https://www.cbsnews.com/news/stars-and-stripes-publisher-editor-separation-notices-pentagon/"/>
+    <hyperlink ref="D180" r:id="rId98" display="https://www.cbsnews.com/news/appeals-court-john-sarcone-letitia-james-federal-prosecutor/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9598,7 +10082,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1016</v>
+        <v>1052</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -9607,7 +10091,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1017</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9765,7 +10249,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1018</v>
+        <v>1054</v>
       </c>
       <c r="B20" s="10" t="n">
         <f aca="false">SUM(B3:B19)</f>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$173</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$185</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="1055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="1085">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1617,6 +1617,15 @@
     <t xml:space="preserve">Aug 21</t>
   </si>
   <si>
+    <t xml:space="preserve">Aug 10, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3181,6 +3190,87 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.cbsnews.com/news/appeals-court-john-sarcone-letitia-james-federal-prosecutor/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicaid will stop paying for some gender-affirming care for transgender minors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/medicaid-stop-paying-gender-affirming-care-transgender-minors-135559574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 11, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appeals court dodges major ruling on Trump’s contentious use of obscure deportation law</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/immigration/appeals-court-trump-alien-enemies-act-tren-de-aragua-venezuela-rcna592435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 13, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kennedy Center board votes to add president’s name again — and throw in a ‘Trump Plaza’</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/trump-administration/kennedy-center-board-votes-partially-close-arts-center-renovations-add-rcna592355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haitians in Ohio who lost protected status get ankle monitors instead of ICE detention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/immigration/haitians-ohio-lost-protected-status-get-ankle-monitors-instead-ice-det-rcna591989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How Trump's construction projects are changing Washington and costing taxpayers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/show/how-trumps-construction-projects-are-changing-washington-and-costing-taxpayers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOJ deploys tactic to strip naturalized Americans of citizenship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/show/doj-deploys-tactic-to-strip-naturalized-americans-of-citizenship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump White House says it's losing $19B-$26 billion a year in revenue as countries dodge tariffs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/politics/trump-white-house-says-its-losing-19b-26-billion-a-year-in-revenue-as-countries-dodge-tariffs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump dismisses military families’ concerns about grim conditions on USS Lincoln</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/donald-trump/trump-dismisses-concerns-family-members-grim-conditions-uss-abraham-li-rcna592598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 14, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump asks Supreme Court to allow White House ballroom construction to continue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/supreme-court/trump-appeals-supreme-court-white-house-ballroom-rcna266912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judge drops Nevada case against electors accused of forging certificate in 2020 election</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/judge-drops-nevada-case-electors-accused-forging-certificate-135627356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump's vaccine order would require millions of individual shots last used decades ago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/health/trumps-vaccine-order-would-require-millions-of-individual-shots-last-used-decades-ago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WATCH: Trump says USS Lincoln's deployment was 'not nearly long enough'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/politics/watch-trump-says-uss-lincolns-deployment-was-not-nearly-long-enough</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -3662,7 +3752,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F173"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -6920,7 +7010,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="5" t="s">
         <v>524</v>
       </c>
@@ -6934,7 +7024,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="5" t="s">
         <v>524</v>
       </c>
@@ -6948,7 +7038,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="5" t="s">
         <v>524</v>
       </c>
@@ -6962,7 +7052,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="5" t="s">
         <v>524</v>
       </c>
@@ -6976,7 +7066,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="5" t="s">
         <v>524</v>
       </c>
@@ -6990,7 +7080,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="5" t="s">
         <v>524</v>
       </c>
@@ -7004,7 +7094,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="5" t="s">
         <v>524</v>
       </c>
@@ -7018,7 +7108,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="5" t="s">
         <v>524</v>
       </c>
@@ -7032,8 +7122,176 @@
         <v>171</v>
       </c>
     </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C174" s="4"/>
+      <c r="D174" s="4"/>
+      <c r="E174" s="4"/>
+      <c r="F174" s="4" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C175" s="4"/>
+      <c r="D175" s="4"/>
+      <c r="E175" s="4"/>
+      <c r="F175" s="4" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C176" s="4"/>
+      <c r="D176" s="4"/>
+      <c r="E176" s="4"/>
+      <c r="F176" s="4" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C177" s="4"/>
+      <c r="D177" s="4"/>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C178" s="4"/>
+      <c r="D178" s="4"/>
+      <c r="E178" s="4"/>
+      <c r="F178" s="4" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C179" s="4"/>
+      <c r="D179" s="4"/>
+      <c r="E179" s="4"/>
+      <c r="F179" s="4" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C180" s="4"/>
+      <c r="D180" s="4"/>
+      <c r="E180" s="4"/>
+      <c r="F180" s="4" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C181" s="4"/>
+      <c r="D181" s="4"/>
+      <c r="E181" s="4"/>
+      <c r="F181" s="4" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C182" s="4"/>
+      <c r="D182" s="4"/>
+      <c r="E182" s="4"/>
+      <c r="F182" s="4" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C183" s="4"/>
+      <c r="D183" s="4"/>
+      <c r="E183" s="4"/>
+      <c r="F183" s="4" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C184" s="4"/>
+      <c r="D184" s="4"/>
+      <c r="E184" s="4"/>
+      <c r="F184" s="4" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C185" s="4"/>
+      <c r="D185" s="4"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="4" t="n">
+        <v>183</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F173"/>
+  <autoFilter ref="A2:F185"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -7053,7 +7311,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E180"/>
+  <dimension ref="A1:E192"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -7064,7 +7322,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7073,19 +7331,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7093,14 +7351,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7108,14 +7366,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7123,14 +7381,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7138,14 +7396,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7153,14 +7411,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7168,14 +7426,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7183,14 +7441,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7198,14 +7456,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7213,14 +7471,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7228,14 +7486,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7243,14 +7501,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7258,14 +7516,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7273,14 +7531,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7288,14 +7546,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7303,14 +7561,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7318,14 +7576,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7333,14 +7591,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7348,14 +7606,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7363,14 +7621,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7378,14 +7636,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7393,14 +7651,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7408,14 +7666,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7423,14 +7681,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7438,14 +7696,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7453,14 +7711,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7468,14 +7726,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7483,14 +7741,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7498,14 +7756,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7513,14 +7771,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7528,14 +7786,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7543,14 +7801,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7558,14 +7816,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7573,14 +7831,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7588,14 +7846,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7603,14 +7861,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7618,14 +7876,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7633,14 +7891,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7648,14 +7906,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7663,10 +7921,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -7678,14 +7936,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7693,14 +7951,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7708,14 +7966,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7723,14 +7981,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7738,14 +7996,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7753,14 +8011,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7768,14 +8026,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7783,14 +8041,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7798,14 +8056,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7813,14 +8071,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7828,14 +8086,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7843,14 +8101,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7858,14 +8116,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7873,14 +8131,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7888,14 +8146,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7903,14 +8161,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7918,14 +8176,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7933,14 +8191,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7948,14 +8206,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7963,14 +8221,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7978,14 +8236,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7993,14 +8251,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8008,14 +8266,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8023,14 +8281,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8038,14 +8296,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8053,14 +8311,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8068,14 +8326,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8083,14 +8341,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8098,14 +8356,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8113,14 +8371,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8128,14 +8386,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8143,14 +8401,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8158,14 +8416,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8173,14 +8431,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8188,14 +8446,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8203,14 +8461,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8218,14 +8476,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8233,14 +8491,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8248,14 +8506,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8263,14 +8521,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8278,16 +8536,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8295,16 +8553,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8312,13 +8570,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -8329,13 +8587,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -8346,16 +8604,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8363,16 +8621,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8380,16 +8638,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D88" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>785</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8397,16 +8655,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8414,16 +8672,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8431,16 +8689,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D91" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>795</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8448,16 +8706,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8465,16 +8723,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D93" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>801</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8482,16 +8740,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8499,16 +8757,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8516,16 +8774,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8533,16 +8791,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>811</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8550,16 +8808,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8567,16 +8825,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8584,16 +8842,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8601,16 +8859,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8618,16 +8876,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8635,16 +8893,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8652,13 +8910,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -8669,16 +8927,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8686,16 +8944,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8703,16 +8961,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8720,16 +8978,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8737,13 +8995,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -8754,13 +9012,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -8771,16 +9029,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8788,16 +9046,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8805,13 +9063,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -8822,16 +9080,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8839,16 +9097,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8856,16 +9114,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8873,16 +9131,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8890,13 +9148,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -8907,16 +9165,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8924,16 +9182,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8941,16 +9199,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8958,16 +9216,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8975,13 +9233,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -8992,13 +9250,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -9009,16 +9267,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9026,16 +9284,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="D126" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="E126" s="5" t="s">
         <v>901</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9043,16 +9301,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9060,16 +9318,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9077,16 +9335,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9094,16 +9352,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C130" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="D130" s="6" t="s">
         <v>914</v>
       </c>
-      <c r="D130" s="6" t="s">
-        <v>911</v>
-      </c>
       <c r="E130" s="5" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9111,13 +9369,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -9128,16 +9386,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9145,16 +9403,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="D133" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="E133" s="5" t="s">
         <v>924</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9162,16 +9420,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9179,16 +9437,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9196,13 +9454,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -9213,13 +9471,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -9230,16 +9488,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9247,16 +9505,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9264,13 +9522,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -9281,16 +9539,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9298,16 +9556,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9315,13 +9573,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -9332,16 +9590,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9349,13 +9607,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -9366,16 +9624,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9383,16 +9641,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9400,16 +9658,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9417,13 +9675,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -9434,13 +9692,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -9451,16 +9709,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9468,16 +9726,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9485,16 +9743,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9502,16 +9760,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9519,16 +9777,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9536,16 +9794,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9553,14 +9811,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9568,16 +9826,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D158" s="6" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E158" s="5" t="s">
         <v>999</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9585,16 +9843,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9602,16 +9860,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9619,16 +9877,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C161" s="5" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>1005</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9636,16 +9894,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9653,16 +9911,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9670,16 +9928,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9687,16 +9945,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9704,13 +9962,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -9721,237 +9979,441 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="5" t="n">
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="5" t="n">
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="5" t="n">
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="5" t="n">
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C171" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>1029</v>
       </c>
-      <c r="D171" s="6" t="s">
-        <v>1030</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="5" t="n">
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="5" t="n">
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="5" t="n">
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="5" t="n">
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C175" s="5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>1039</v>
       </c>
-      <c r="D175" s="6" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="5" t="n">
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="5" t="n">
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="5" t="n">
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C178" s="5" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>1046</v>
       </c>
-      <c r="D178" s="6" t="s">
-        <v>1047</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="5" t="n">
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="5" t="n">
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1043</v>
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E181" s="5" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E182" s="5" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="5" t="n">
+        <v>174</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E183" s="5" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E184" s="5" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="5" t="n">
+        <v>176</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E185" s="5" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E186" s="5" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E187" s="5" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E188" s="5" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E189" s="5" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E190" s="5" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="5" t="n">
+        <v>182</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E191" s="5" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E192" s="5" t="s">
+        <v>1073</v>
       </c>
     </row>
   </sheetData>
@@ -10057,6 +10519,18 @@
     <hyperlink ref="D178" r:id="rId96" display="https://www.nbcnews.com/politics/trump-administration/navy-discusses-renaming-aircraft-carrier-trump-black-uss-doris-miller-rcna593667"/>
     <hyperlink ref="D179" r:id="rId97" display="https://www.cbsnews.com/news/stars-and-stripes-publisher-editor-separation-notices-pentagon/"/>
     <hyperlink ref="D180" r:id="rId98" display="https://www.cbsnews.com/news/appeals-court-john-sarcone-letitia-james-federal-prosecutor/"/>
+    <hyperlink ref="D181" r:id="rId99" display="https://abcnews.com/Politics/wireStory/medicaid-stop-paying-gender-affirming-care-transgender-minors-135559574"/>
+    <hyperlink ref="D182" r:id="rId100" display="https://www.nbcnews.com/politics/immigration/appeals-court-trump-alien-enemies-act-tren-de-aragua-venezuela-rcna592435"/>
+    <hyperlink ref="D183" r:id="rId101" display="https://www.nbcnews.com/politics/trump-administration/kennedy-center-board-votes-partially-close-arts-center-renovations-add-rcna592355"/>
+    <hyperlink ref="D184" r:id="rId102" display="https://www.nbcnews.com/politics/immigration/haitians-ohio-lost-protected-status-get-ankle-monitors-instead-ice-det-rcna591989"/>
+    <hyperlink ref="D185" r:id="rId103" display="https://www.pbs.org/newshour/show/how-trumps-construction-projects-are-changing-washington-and-costing-taxpayers"/>
+    <hyperlink ref="D186" r:id="rId104" display="https://www.pbs.org/newshour/show/doj-deploys-tactic-to-strip-naturalized-americans-of-citizenship"/>
+    <hyperlink ref="D187" r:id="rId105" display="https://www.pbs.org/newshour/politics/trump-white-house-says-its-losing-19b-26-billion-a-year-in-revenue-as-countries-dodge-tariffs"/>
+    <hyperlink ref="D188" r:id="rId106" display="https://www.nbcnews.com/politics/donald-trump/trump-dismisses-concerns-family-members-grim-conditions-uss-abraham-li-rcna592598"/>
+    <hyperlink ref="D189" r:id="rId107" display="https://www.nbcnews.com/politics/supreme-court/trump-appeals-supreme-court-white-house-ballroom-rcna266912"/>
+    <hyperlink ref="D190" r:id="rId108" display="https://abcnews.com/Politics/wireStory/judge-drops-nevada-case-electors-accused-forging-certificate-135627356"/>
+    <hyperlink ref="D191" r:id="rId109" display="https://www.pbs.org/newshour/health/trumps-vaccine-order-would-require-millions-of-individual-shots-last-used-decades-ago"/>
+    <hyperlink ref="D192" r:id="rId110" display="https://www.pbs.org/newshour/politics/watch-trump-says-uss-lincolns-deployment-was-not-nearly-long-enough"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10082,7 +10556,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1052</v>
+        <v>1082</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -10091,7 +10565,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1053</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10249,7 +10723,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1054</v>
+        <v>1084</v>
       </c>
       <c r="B20" s="10" t="n">
         <f aca="false">SUM(B3:B19)</f>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$185</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$191</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="1085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="1103">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1626,6 +1626,18 @@
     <t xml:space="preserve">Aug 14</t>
   </si>
   <si>
+    <t xml:space="preserve">Aug 3, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 7</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3271,6 +3283,48 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.pbs.org/newshour/politics/watch-trump-says-uss-lincolns-deployment-was-not-nearly-long-enough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">States sue to block feds from sharing personal data of millions who receive social service benefits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/states-sue-block-feds-sharing-personal-data-millions-135335305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empty pews and fear of ICE on Maryland’s Eastern Shore after TPS ends for Haitians</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/empty-pews-fear-ice-marylands-eastern-shore-after-135382907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 5, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump says he’ll appeal decision halting ballroom construction to the Supreme Court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/white-house/appeals-court-blocks-trump-ballroom-construction-rcna591376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 7, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With their assault on science, Trumpists aren’t just harming America – they’re harming themselves | Jan-Werner Müller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/commentisfree/2026/aug/07/trump-scientific-research-universities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICE will only release body camera video when in agency's 'best interests,' policy says</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/nation/ice-will-only-release-body-camera-video-when-in-agencys-best-interests-policy-says</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump administration proceeds with efforts to fire Federal Reserve governor Lisa Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/politics/trump-administration-proceeds-with-efforts-to-fire-federal-reserve-governor-lisa-cook</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -3752,7 +3806,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -7122,7 +7176,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="4" t="s">
         <v>530</v>
       </c>
@@ -7136,7 +7190,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="4" t="s">
         <v>530</v>
       </c>
@@ -7150,7 +7204,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="4" t="s">
         <v>530</v>
       </c>
@@ -7164,7 +7218,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="4" t="s">
         <v>530</v>
       </c>
@@ -7178,7 +7232,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="4" t="s">
         <v>530</v>
       </c>
@@ -7192,7 +7246,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="4" t="s">
         <v>530</v>
       </c>
@@ -7206,7 +7260,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="4" t="s">
         <v>530</v>
       </c>
@@ -7220,7 +7274,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="4" t="s">
         <v>530</v>
       </c>
@@ -7234,7 +7288,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="4" t="s">
         <v>530</v>
       </c>
@@ -7248,7 +7302,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="4" t="s">
         <v>530</v>
       </c>
@@ -7262,7 +7316,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="4" t="s">
         <v>530</v>
       </c>
@@ -7276,7 +7330,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="4" t="s">
         <v>530</v>
       </c>
@@ -7290,8 +7344,92 @@
         <v>183</v>
       </c>
     </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="C186" s="5"/>
+      <c r="D186" s="5"/>
+      <c r="E186" s="5"/>
+      <c r="F186" s="5" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="C187" s="5"/>
+      <c r="D187" s="5"/>
+      <c r="E187" s="5"/>
+      <c r="F187" s="5" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="C188" s="5"/>
+      <c r="D188" s="5"/>
+      <c r="E188" s="5"/>
+      <c r="F188" s="5" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="C189" s="5"/>
+      <c r="D189" s="5"/>
+      <c r="E189" s="5"/>
+      <c r="F189" s="5" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="C190" s="5"/>
+      <c r="D190" s="5"/>
+      <c r="E190" s="5"/>
+      <c r="F190" s="5" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="C191" s="5"/>
+      <c r="D191" s="5"/>
+      <c r="E191" s="5"/>
+      <c r="F191" s="5" t="n">
+        <v>189</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F185"/>
+  <autoFilter ref="A2:F191"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -7311,7 +7449,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E192"/>
+  <dimension ref="A1:E198"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -7322,7 +7460,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7331,19 +7469,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7351,14 +7489,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7366,14 +7504,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7381,14 +7519,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7396,14 +7534,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7411,14 +7549,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7426,14 +7564,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7441,14 +7579,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7456,14 +7594,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7471,14 +7609,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7486,14 +7624,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7501,14 +7639,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7516,14 +7654,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7531,14 +7669,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7546,14 +7684,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7561,14 +7699,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7576,14 +7714,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7591,14 +7729,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7606,14 +7744,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7621,14 +7759,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7636,14 +7774,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7651,14 +7789,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7666,14 +7804,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7681,14 +7819,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7696,14 +7834,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7711,14 +7849,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7726,14 +7864,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7741,14 +7879,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7756,14 +7894,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7771,14 +7909,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7786,14 +7924,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7801,14 +7939,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7816,14 +7954,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7831,14 +7969,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7846,14 +7984,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7861,14 +7999,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7876,14 +8014,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7891,14 +8029,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7906,14 +8044,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7921,10 +8059,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -7936,14 +8074,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7951,14 +8089,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7966,14 +8104,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7981,14 +8119,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7996,14 +8134,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8011,14 +8149,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8026,14 +8164,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8041,14 +8179,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8056,14 +8194,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8071,14 +8209,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8086,14 +8224,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8101,14 +8239,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8116,14 +8254,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8131,14 +8269,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8146,14 +8284,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8161,14 +8299,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8176,14 +8314,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8191,14 +8329,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8206,14 +8344,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8221,14 +8359,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8236,14 +8374,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8251,14 +8389,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8266,14 +8404,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8281,14 +8419,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8296,14 +8434,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8311,14 +8449,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8326,14 +8464,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8341,14 +8479,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8356,14 +8494,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8371,14 +8509,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8386,14 +8524,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8401,14 +8539,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8416,14 +8554,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8431,14 +8569,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8446,14 +8584,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8461,14 +8599,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8476,14 +8614,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8491,14 +8629,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8506,14 +8644,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8521,14 +8659,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8536,16 +8674,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8553,16 +8691,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8570,13 +8708,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -8587,13 +8725,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -8604,16 +8742,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8621,16 +8759,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8638,16 +8776,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8655,16 +8793,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>789</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>790</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8672,16 +8810,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8689,16 +8827,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8706,16 +8844,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8723,16 +8861,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8740,16 +8878,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8757,16 +8895,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8774,16 +8912,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8791,16 +8929,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C97" s="5" t="s">
+        <v>819</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>820</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>815</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>816</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8808,16 +8946,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8825,16 +8963,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8842,16 +8980,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8859,16 +8997,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8876,16 +9014,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8893,16 +9031,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8910,13 +9048,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -8927,16 +9065,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8944,16 +9082,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8961,16 +9099,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8978,16 +9116,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8995,13 +9133,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -9012,13 +9150,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -9029,16 +9167,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9046,16 +9184,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9063,13 +9201,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -9080,16 +9218,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9097,16 +9235,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9114,16 +9252,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9131,16 +9269,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9148,13 +9286,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -9165,16 +9303,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9182,16 +9320,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9199,16 +9337,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="E121" s="5" t="s">
         <v>888</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>889</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>890</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9216,16 +9354,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9233,13 +9371,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -9250,13 +9388,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -9267,16 +9405,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9284,16 +9422,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9301,16 +9439,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9318,16 +9456,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9335,16 +9473,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9352,16 +9490,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9369,13 +9507,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -9386,16 +9524,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9403,16 +9541,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9420,16 +9558,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9437,16 +9575,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9454,13 +9592,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -9471,13 +9609,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -9488,16 +9626,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9505,16 +9643,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9522,13 +9660,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -9539,16 +9677,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9556,16 +9694,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9573,13 +9711,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -9590,16 +9728,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9607,13 +9745,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -9624,16 +9762,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9641,16 +9779,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9658,16 +9796,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9675,13 +9813,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -9692,13 +9830,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -9709,16 +9847,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9726,16 +9864,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9743,16 +9881,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9760,16 +9898,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9777,16 +9915,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9794,16 +9932,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9811,14 +9949,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9826,16 +9964,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9843,16 +9981,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9860,16 +9998,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9877,16 +10015,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="D161" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>1009</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9894,16 +10032,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9911,16 +10049,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9928,16 +10066,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9945,16 +10083,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9962,13 +10100,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -9979,16 +10117,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9996,13 +10134,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -10013,16 +10151,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10030,16 +10168,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10047,16 +10185,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D171" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>1033</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10064,16 +10202,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10081,16 +10219,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10098,16 +10236,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10115,16 +10253,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="D175" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>1043</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10132,16 +10270,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10149,16 +10287,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10166,16 +10304,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D178" s="6" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>1050</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10183,16 +10321,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10200,220 +10338,322 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="5" t="n">
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="182" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="5" t="n">
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="183" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="5" t="n">
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="5" t="n">
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="D184" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E184" s="5" t="s">
         <v>1064</v>
       </c>
-      <c r="E184" s="5" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="5" t="n">
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="5" t="n">
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="187" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="5" t="n">
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="5" t="n">
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="5" t="n">
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="190" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="5" t="n">
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="D190" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E190" s="5" t="s">
         <v>1077</v>
       </c>
-      <c r="E190" s="5" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="191" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="5" t="n">
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="5" t="n">
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1073</v>
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E193" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E194" s="5" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="5" t="n">
+        <v>186</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E195" s="5" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="5" t="n">
+        <v>187</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E196" s="5" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E197" s="5" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="5" t="n">
+        <v>189</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E198" s="5" t="s">
+        <v>1093</v>
       </c>
     </row>
   </sheetData>
@@ -10531,6 +10771,12 @@
     <hyperlink ref="D190" r:id="rId108" display="https://abcnews.com/Politics/wireStory/judge-drops-nevada-case-electors-accused-forging-certificate-135627356"/>
     <hyperlink ref="D191" r:id="rId109" display="https://www.pbs.org/newshour/health/trumps-vaccine-order-would-require-millions-of-individual-shots-last-used-decades-ago"/>
     <hyperlink ref="D192" r:id="rId110" display="https://www.pbs.org/newshour/politics/watch-trump-says-uss-lincolns-deployment-was-not-nearly-long-enough"/>
+    <hyperlink ref="D193" r:id="rId111" display="https://abcnews.com/Politics/wireStory/states-sue-block-feds-sharing-personal-data-millions-135335305"/>
+    <hyperlink ref="D194" r:id="rId112" display="https://abcnews.com/Politics/wireStory/empty-pews-fear-ice-marylands-eastern-shore-after-135382907"/>
+    <hyperlink ref="D195" r:id="rId113" display="https://www.nbcnews.com/politics/white-house/appeals-court-blocks-trump-ballroom-construction-rcna591376"/>
+    <hyperlink ref="D196" r:id="rId114" display="https://www.theguardian.com/commentisfree/2026/aug/07/trump-scientific-research-universities"/>
+    <hyperlink ref="D197" r:id="rId115" display="https://www.pbs.org/newshour/nation/ice-will-only-release-body-camera-video-when-in-agencys-best-interests-policy-says"/>
+    <hyperlink ref="D198" r:id="rId116" display="https://www.pbs.org/newshour/politics/trump-administration-proceeds-with-efforts-to-fire-federal-reserve-governor-lisa-cook"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10556,7 +10802,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1082</v>
+        <v>1100</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -10565,7 +10811,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1083</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10723,7 +10969,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1084</v>
+        <v>1102</v>
       </c>
       <c r="B20" s="10" t="n">
         <f aca="false">SUM(B3:B19)</f>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$191</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$197</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="1121">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1638,6 +1638,15 @@
     <t xml:space="preserve">Aug 7</t>
   </si>
   <si>
+    <t xml:space="preserve">Jul 27, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 31</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3325,6 +3334,51 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.pbs.org/newshour/politics/trump-administration-proceeds-with-efforts-to-fire-federal-reserve-governor-lisa-cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuesday referendum tests GOP push to restrict citizen-led ballot initiatives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.npr.org/2026/08/01/nx-s1-5911949/tuesday-referendum-tests-gop-push-to-restrict-citizen-led-ballot-initiatives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 1, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More than 25,000 children lose previous legal protections, as federal contract ends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.npr.org/2026/08/01/nx-s1-5913679/immgirant-children-lawyers-trump-administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump rebukes Jeanine Pirro over decision to drop Reflecting Pool vandalism case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/trump-administration/trump-rebukes-jeanine-pirro-decision-drop-reflecting-pool-vandalism-ca-rcna590408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. strikes Iran after Trump reportedly issues menacing new threat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/world/middle-east/us-thwarts-iranian-missile-attack-launches-strikes-saudi-arabia-rcna589773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 29, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump asks Supreme Court to overturn $83.3 million award in E. Jean Carroll defamation case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/donald-trump/trump-asks-supreme-court-overturn-833-million-award-e-jean-carroll-def-rcna589762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump appeals ruling that found his $10B IRS suit aimed to ‘manipulate’ legal proceedings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/donald-trump/appeals-ruling-found-10-billion-irs-suit-aimed-manipulate-legal-rcna590307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 31, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -3806,7 +3860,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F197"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -7344,7 +7398,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="5" t="s">
         <v>533</v>
       </c>
@@ -7358,7 +7412,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="5" t="s">
         <v>533</v>
       </c>
@@ -7372,7 +7426,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="5" t="s">
         <v>533</v>
       </c>
@@ -7386,7 +7440,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="5" t="s">
         <v>533</v>
       </c>
@@ -7400,7 +7454,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="5" t="s">
         <v>533</v>
       </c>
@@ -7414,7 +7468,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="5" t="s">
         <v>533</v>
       </c>
@@ -7428,8 +7482,92 @@
         <v>189</v>
       </c>
     </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C192" s="4"/>
+      <c r="D192" s="4"/>
+      <c r="E192" s="4"/>
+      <c r="F192" s="4" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C193" s="4"/>
+      <c r="D193" s="4"/>
+      <c r="E193" s="4"/>
+      <c r="F193" s="4" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C194" s="4"/>
+      <c r="D194" s="4"/>
+      <c r="E194" s="4"/>
+      <c r="F194" s="4" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="C195" s="4"/>
+      <c r="D195" s="4"/>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="C196" s="4"/>
+      <c r="D196" s="4"/>
+      <c r="E196" s="4"/>
+      <c r="F196" s="4" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="C197" s="4"/>
+      <c r="D197" s="4"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4" t="n">
+        <v>195</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F191"/>
+  <autoFilter ref="A2:F197"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -7449,7 +7587,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E198"/>
+  <dimension ref="A1:E204"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -7460,7 +7598,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7469,19 +7607,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7489,14 +7627,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7504,14 +7642,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7519,14 +7657,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7534,14 +7672,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7549,14 +7687,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7564,14 +7702,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7579,14 +7717,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7594,14 +7732,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7609,14 +7747,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7624,14 +7762,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7639,14 +7777,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7654,14 +7792,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7669,14 +7807,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7684,14 +7822,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7699,14 +7837,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7714,14 +7852,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7729,14 +7867,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7744,14 +7882,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7759,14 +7897,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7774,14 +7912,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7789,14 +7927,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7804,14 +7942,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7819,14 +7957,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7834,14 +7972,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7849,14 +7987,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7864,14 +8002,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7879,14 +8017,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7894,14 +8032,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7909,14 +8047,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7924,14 +8062,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7939,14 +8077,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7954,14 +8092,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7969,14 +8107,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7984,14 +8122,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7999,14 +8137,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8014,14 +8152,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8029,14 +8167,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8044,14 +8182,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8059,10 +8197,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -8074,14 +8212,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8089,14 +8227,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8104,14 +8242,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8119,14 +8257,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8134,14 +8272,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8149,14 +8287,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8164,14 +8302,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8179,14 +8317,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8194,14 +8332,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8209,14 +8347,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8224,14 +8362,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8239,14 +8377,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8254,14 +8392,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8269,14 +8407,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8284,14 +8422,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8299,14 +8437,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8314,14 +8452,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8329,14 +8467,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8344,14 +8482,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8359,14 +8497,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8374,14 +8512,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8389,14 +8527,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8404,14 +8542,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8419,14 +8557,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8434,14 +8572,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8449,14 +8587,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8464,14 +8602,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8479,14 +8617,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8494,14 +8632,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8509,14 +8647,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8524,14 +8662,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8539,14 +8677,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8554,14 +8692,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8569,14 +8707,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8584,14 +8722,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8599,14 +8737,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8614,14 +8752,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8629,14 +8767,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8644,14 +8782,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8659,14 +8797,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8674,16 +8812,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8691,16 +8829,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8708,13 +8846,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -8725,13 +8863,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -8742,16 +8880,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8759,16 +8897,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8776,16 +8914,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="D88" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>792</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8793,16 +8931,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8810,16 +8948,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8827,16 +8965,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D91" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>802</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8844,16 +8982,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8861,16 +8999,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="D93" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>808</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8878,16 +9016,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8895,16 +9033,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8912,16 +9050,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8929,16 +9067,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>823</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>818</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>819</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>820</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8946,16 +9084,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8963,16 +9101,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8980,16 +9118,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8997,16 +9135,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9014,16 +9152,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9031,16 +9169,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9048,13 +9186,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -9065,16 +9203,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9082,16 +9220,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9099,16 +9237,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9116,16 +9254,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9133,13 +9271,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -9150,13 +9288,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -9167,16 +9305,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9184,16 +9322,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9201,13 +9339,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -9218,16 +9356,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9235,16 +9373,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9252,16 +9390,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9269,16 +9407,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9286,13 +9424,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -9303,16 +9441,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9320,16 +9458,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9337,16 +9475,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9354,16 +9492,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9371,13 +9509,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -9388,13 +9526,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -9405,16 +9543,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9422,16 +9560,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D126" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="E126" s="5" t="s">
         <v>908</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9439,16 +9577,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9456,16 +9594,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9473,16 +9611,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9490,16 +9628,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C130" s="5" t="s">
+        <v>924</v>
+      </c>
+      <c r="D130" s="6" t="s">
         <v>921</v>
       </c>
-      <c r="D130" s="6" t="s">
-        <v>918</v>
-      </c>
       <c r="E130" s="5" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9507,13 +9645,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -9524,16 +9662,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9541,16 +9679,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="D133" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="E133" s="5" t="s">
         <v>931</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9558,16 +9696,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9575,16 +9713,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9592,13 +9730,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -9609,13 +9747,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -9626,16 +9764,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9643,16 +9781,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9660,13 +9798,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -9677,16 +9815,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9694,16 +9832,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9711,13 +9849,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -9728,16 +9866,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9745,13 +9883,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -9762,16 +9900,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9779,16 +9917,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9796,16 +9934,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9813,13 +9951,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -9830,13 +9968,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -9847,16 +9985,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9864,16 +10002,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9881,16 +10019,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9898,16 +10036,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9915,16 +10053,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9932,16 +10070,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9949,14 +10087,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9964,16 +10102,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="D158" s="6" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E158" s="5" t="s">
         <v>1006</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9981,16 +10119,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9998,16 +10136,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10015,16 +10153,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C161" s="5" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>1012</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10032,16 +10170,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10049,16 +10187,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10066,16 +10204,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10083,16 +10221,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10100,13 +10238,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -10117,16 +10255,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10134,13 +10272,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -10151,16 +10289,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10168,16 +10306,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10185,16 +10323,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C171" s="5" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>1036</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>1037</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10202,16 +10340,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10219,16 +10357,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10236,16 +10374,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10253,16 +10391,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C175" s="5" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>1046</v>
-      </c>
-      <c r="D175" s="6" t="s">
-        <v>1047</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10270,16 +10408,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10287,16 +10425,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10304,16 +10442,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C178" s="5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>1053</v>
-      </c>
-      <c r="D178" s="6" t="s">
-        <v>1054</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10321,16 +10459,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10338,16 +10476,16 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10355,16 +10493,16 @@
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10372,16 +10510,16 @@
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10389,16 +10527,16 @@
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10406,16 +10544,16 @@
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C184" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E184" s="5" t="s">
         <v>1067</v>
-      </c>
-      <c r="D184" s="6" t="s">
-        <v>1068</v>
-      </c>
-      <c r="E184" s="5" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10423,16 +10561,16 @@
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10440,16 +10578,16 @@
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10457,16 +10595,16 @@
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10474,16 +10612,16 @@
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10491,16 +10629,16 @@
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10508,16 +10646,16 @@
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C190" s="5" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E190" s="5" t="s">
         <v>1080</v>
-      </c>
-      <c r="D190" s="6" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10525,16 +10663,16 @@
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10542,118 +10680,220 @@
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="193" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="5" t="n">
         <v>184</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="5" t="n">
         <v>185</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="5" t="n">
         <v>186</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="196" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="5" t="n">
         <v>187</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="5" t="n">
         <v>188</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C197" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E197" s="5" t="s">
         <v>1096</v>
       </c>
-      <c r="D197" s="6" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="198" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="5" t="n">
         <v>189</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>1093</v>
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D199" s="6" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E199" s="5" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E200" s="5" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E201" s="5" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="5" t="n">
+        <v>193</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="5" t="n">
+        <v>194</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E203" s="5" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D204" s="6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E204" s="5" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -10777,6 +11017,12 @@
     <hyperlink ref="D196" r:id="rId114" display="https://www.theguardian.com/commentisfree/2026/aug/07/trump-scientific-research-universities"/>
     <hyperlink ref="D197" r:id="rId115" display="https://www.pbs.org/newshour/nation/ice-will-only-release-body-camera-video-when-in-agencys-best-interests-policy-says"/>
     <hyperlink ref="D198" r:id="rId116" display="https://www.pbs.org/newshour/politics/trump-administration-proceeds-with-efforts-to-fire-federal-reserve-governor-lisa-cook"/>
+    <hyperlink ref="D199" r:id="rId117" display="https://www.npr.org/2026/08/01/nx-s1-5911949/tuesday-referendum-tests-gop-push-to-restrict-citizen-led-ballot-initiatives"/>
+    <hyperlink ref="D200" r:id="rId118" display="https://www.npr.org/2026/08/01/nx-s1-5913679/immgirant-children-lawyers-trump-administration"/>
+    <hyperlink ref="D201" r:id="rId119" display="https://www.nbcnews.com/politics/trump-administration/trump-rebukes-jeanine-pirro-decision-drop-reflecting-pool-vandalism-ca-rcna590408"/>
+    <hyperlink ref="D202" r:id="rId120" display="https://www.nbcnews.com/world/middle-east/us-thwarts-iranian-missile-attack-launches-strikes-saudi-arabia-rcna589773"/>
+    <hyperlink ref="D203" r:id="rId121" display="https://www.nbcnews.com/politics/donald-trump/trump-asks-supreme-court-overturn-833-million-award-e-jean-carroll-def-rcna589762"/>
+    <hyperlink ref="D204" r:id="rId122" display="https://www.nbcnews.com/politics/donald-trump/appeals-ruling-found-10-billion-irs-suit-aimed-manipulate-legal-rcna590307"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10802,7 +11048,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1100</v>
+        <v>1118</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -10811,7 +11057,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1101</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10969,7 +11215,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1102</v>
+        <v>1120</v>
       </c>
       <c r="B20" s="10" t="n">
         <f aca="false">SUM(B3:B19)</f>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$197</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$205</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="1143">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1647,6 +1647,18 @@
     <t xml:space="preserve">Jul 31</t>
   </si>
   <si>
+    <t xml:space="preserve">Jul 20, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 24</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3379,6 +3391,60 @@
   </si>
   <si>
     <t xml:space="preserve">Jul 31, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The men behind Trump's $3.47 gas: An NFL coach, a GOP fundraiser and two New Jersey brothers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/men-trumps-347-gas-nfl-coach-gop-fundraiser-134918715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh wave of U.S. tariffs takes effect, hitting global trade partners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/business/economy/trump-tariffs-60-countries-forced-labor-rcna588972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 23, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 states sue FEMA and DHS, accuse Trump admin. of withholding funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cbsnews.com/news/states-sue-fema-dhs-trump-administration-funding/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump imposes double-digit tariffs on dozens of countries as stopgap 10% levies expire Friday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/politics/trump-imposes-double-digit-tariffs-on-dozens-of-countries-as-stopgap-10-levies-expire-friday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump administration admits legal errors and withdraws subpoenas of 3 NYT reporters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/politics/trump-administration-admits-legal-errors-and-withdraws-subpoenas-of-3-nyt-reporters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump says he will dismantle the ICC ‘brick by brick’. It could be his most chilling move of all | Steve Bloomfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/commentisfree/2026/jul/24/icc-international-criminal-court-trump-putin-netanyahu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 24, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump orders signs placed outside Smithsonian warning of "inaccurate" information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cbsnews.com/news/trump-smithsonian-museum-warning-signs-inaccurate-information/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sen. Peters wants to know why ICE bought spyware that can take control of phones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cbsnews.com/news/senate-ice-graphite-spyware-phones/</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -3860,7 +3926,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F197"/>
+  <dimension ref="A1:F205"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -7482,7 +7548,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="4" t="s">
         <v>537</v>
       </c>
@@ -7496,7 +7562,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="4" t="s">
         <v>537</v>
       </c>
@@ -7510,7 +7576,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="4" t="s">
         <v>537</v>
       </c>
@@ -7524,7 +7590,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="4" t="s">
         <v>537</v>
       </c>
@@ -7538,7 +7604,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="4" t="s">
         <v>537</v>
       </c>
@@ -7552,7 +7618,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="4" t="s">
         <v>537</v>
       </c>
@@ -7566,8 +7632,120 @@
         <v>195</v>
       </c>
     </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="C198" s="5"/>
+      <c r="D198" s="5"/>
+      <c r="E198" s="5"/>
+      <c r="F198" s="5" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="C199" s="5"/>
+      <c r="D199" s="5"/>
+      <c r="E199" s="5"/>
+      <c r="F199" s="5" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="C200" s="5"/>
+      <c r="D200" s="5"/>
+      <c r="E200" s="5"/>
+      <c r="F200" s="5" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="C201" s="5"/>
+      <c r="D201" s="5"/>
+      <c r="E201" s="5"/>
+      <c r="F201" s="5" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="C202" s="5"/>
+      <c r="D202" s="5"/>
+      <c r="E202" s="5"/>
+      <c r="F202" s="5" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="C203" s="5"/>
+      <c r="D203" s="5"/>
+      <c r="E203" s="5"/>
+      <c r="F203" s="5" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="C204" s="5"/>
+      <c r="D204" s="5"/>
+      <c r="E204" s="5"/>
+      <c r="F204" s="5" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="C205" s="5"/>
+      <c r="D205" s="5"/>
+      <c r="E205" s="5"/>
+      <c r="F205" s="5" t="n">
+        <v>203</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F197"/>
+  <autoFilter ref="A2:F205"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -7587,7 +7765,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E204"/>
+  <dimension ref="A1:E212"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -7598,7 +7776,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7607,19 +7785,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7627,14 +7805,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7642,14 +7820,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7657,14 +7835,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7672,14 +7850,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7687,14 +7865,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7702,14 +7880,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7717,14 +7895,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7732,14 +7910,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7747,14 +7925,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7762,14 +7940,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7777,14 +7955,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7792,14 +7970,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7807,14 +7985,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7822,14 +8000,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7837,14 +8015,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7852,14 +8030,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7867,14 +8045,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7882,14 +8060,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7897,14 +8075,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7912,14 +8090,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7927,14 +8105,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7942,14 +8120,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7957,14 +8135,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7972,14 +8150,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7987,14 +8165,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8002,14 +8180,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8017,14 +8195,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8032,14 +8210,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8047,14 +8225,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8062,14 +8240,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8077,14 +8255,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8092,14 +8270,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8107,14 +8285,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8122,14 +8300,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8137,14 +8315,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8152,14 +8330,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8167,14 +8345,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8182,14 +8360,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8197,10 +8375,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -8212,14 +8390,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8227,14 +8405,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8242,14 +8420,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8257,14 +8435,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8272,14 +8450,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8287,14 +8465,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8302,14 +8480,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8317,14 +8495,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8332,14 +8510,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8347,14 +8525,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8362,14 +8540,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8377,14 +8555,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8392,14 +8570,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8407,14 +8585,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8422,14 +8600,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8437,14 +8615,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8452,14 +8630,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8467,14 +8645,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8482,14 +8660,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8497,14 +8675,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8512,14 +8690,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8527,14 +8705,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8542,14 +8720,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8557,14 +8735,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8572,14 +8750,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8587,14 +8765,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8602,14 +8780,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8617,14 +8795,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8632,14 +8810,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8647,14 +8825,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8662,14 +8840,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8677,14 +8855,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8692,14 +8870,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8707,14 +8885,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8722,14 +8900,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8737,14 +8915,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8752,14 +8930,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8767,14 +8945,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8782,14 +8960,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8797,14 +8975,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8812,16 +8990,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8829,16 +9007,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8846,13 +9024,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -8863,13 +9041,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -8880,16 +9058,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8897,16 +9075,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8914,16 +9092,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8931,16 +9109,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>796</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8948,16 +9126,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8965,16 +9143,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8982,16 +9160,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8999,16 +9177,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9016,16 +9194,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9033,16 +9211,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9050,16 +9228,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9067,16 +9245,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C97" s="5" t="s">
+        <v>826</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>822</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>823</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9084,16 +9262,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9101,16 +9279,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9118,16 +9296,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9135,16 +9313,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9152,16 +9330,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9169,16 +9347,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9186,13 +9364,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -9203,16 +9381,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9220,16 +9398,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9237,16 +9415,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9254,16 +9432,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9271,13 +9449,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -9288,13 +9466,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -9305,16 +9483,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9322,16 +9500,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9339,13 +9517,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -9356,16 +9534,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9373,16 +9551,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9390,16 +9568,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9407,16 +9585,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9424,13 +9602,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -9441,16 +9619,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9458,16 +9636,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9475,16 +9653,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="E121" s="5" t="s">
         <v>895</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>896</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>897</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9492,16 +9670,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9509,13 +9687,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -9526,13 +9704,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -9543,16 +9721,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9560,16 +9738,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9577,16 +9755,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9594,16 +9772,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9611,16 +9789,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9628,16 +9806,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9645,13 +9823,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -9662,16 +9840,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9679,16 +9857,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9696,16 +9874,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9713,16 +9891,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9730,13 +9908,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -9747,13 +9925,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -9764,16 +9942,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9781,16 +9959,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9798,13 +9976,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -9815,16 +9993,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9832,16 +10010,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9849,13 +10027,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -9866,16 +10044,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9883,13 +10061,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -9900,16 +10078,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9917,16 +10095,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9934,16 +10112,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9951,13 +10129,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -9968,13 +10146,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -9985,16 +10163,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10002,16 +10180,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10019,16 +10197,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10036,16 +10214,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10053,16 +10231,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10070,16 +10248,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10087,14 +10265,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10102,16 +10280,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10119,16 +10297,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10136,16 +10314,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10153,16 +10331,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="D161" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>1016</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10170,16 +10348,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10187,16 +10365,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10204,16 +10382,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10221,16 +10399,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10238,13 +10416,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -10255,16 +10433,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10272,13 +10450,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -10289,16 +10467,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10306,16 +10484,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10323,16 +10501,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="D171" s="6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>1040</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10340,16 +10518,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10357,16 +10535,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10374,16 +10552,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10391,16 +10569,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D175" s="6" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>1050</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10408,16 +10586,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10425,16 +10603,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10442,16 +10620,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="D178" s="6" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>1057</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10459,16 +10637,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10476,16 +10654,16 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10493,16 +10671,16 @@
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10510,16 +10688,16 @@
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10527,16 +10705,16 @@
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10544,16 +10722,16 @@
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="D184" s="6" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E184" s="5" t="s">
         <v>1071</v>
-      </c>
-      <c r="E184" s="5" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10561,16 +10739,16 @@
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10578,16 +10756,16 @@
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10595,16 +10773,16 @@
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10612,16 +10790,16 @@
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10629,16 +10807,16 @@
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10646,16 +10824,16 @@
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="D190" s="6" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E190" s="5" t="s">
         <v>1084</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10663,16 +10841,16 @@
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10680,16 +10858,16 @@
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10697,13 +10875,13 @@
         <v>184</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>533</v>
@@ -10714,16 +10892,16 @@
         <v>185</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10731,16 +10909,16 @@
         <v>186</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10748,16 +10926,16 @@
         <v>187</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10765,16 +10943,16 @@
         <v>188</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="D197" s="6" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E197" s="5" t="s">
         <v>1100</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10782,118 +10960,254 @@
         <v>189</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="5" t="n">
         <v>190</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="5" t="n">
         <v>191</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="5" t="n">
         <v>192</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="D201" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E201" s="5" t="s">
         <v>1109</v>
       </c>
-      <c r="E201" s="5" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="5" t="n">
         <v>193</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="203" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="5" t="n">
         <v>194</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="204" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="5" t="n">
         <v>195</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1117</v>
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E205" s="5" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="5" t="n">
+        <v>197</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E206" s="5" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>880</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E207" s="5" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E208" s="5" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E209" s="5" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="5" t="n">
+        <v>201</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E210" s="5" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="5" t="n">
+        <v>202</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>880</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E211" s="5" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>880</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E212" s="5" t="s">
+        <v>1135</v>
       </c>
     </row>
   </sheetData>
@@ -11023,6 +11337,14 @@
     <hyperlink ref="D202" r:id="rId120" display="https://www.nbcnews.com/world/middle-east/us-thwarts-iranian-missile-attack-launches-strikes-saudi-arabia-rcna589773"/>
     <hyperlink ref="D203" r:id="rId121" display="https://www.nbcnews.com/politics/donald-trump/trump-asks-supreme-court-overturn-833-million-award-e-jean-carroll-def-rcna589762"/>
     <hyperlink ref="D204" r:id="rId122" display="https://www.nbcnews.com/politics/donald-trump/appeals-ruling-found-10-billion-irs-suit-aimed-manipulate-legal-rcna590307"/>
+    <hyperlink ref="D205" r:id="rId123" display="https://abcnews.com/Politics/wireStory/men-trumps-347-gas-nfl-coach-gop-fundraiser-134918715"/>
+    <hyperlink ref="D206" r:id="rId124" display="https://www.nbcnews.com/business/economy/trump-tariffs-60-countries-forced-labor-rcna588972"/>
+    <hyperlink ref="D207" r:id="rId125" display="https://www.cbsnews.com/news/states-sue-fema-dhs-trump-administration-funding/"/>
+    <hyperlink ref="D208" r:id="rId126" display="https://www.pbs.org/newshour/politics/trump-imposes-double-digit-tariffs-on-dozens-of-countries-as-stopgap-10-levies-expire-friday"/>
+    <hyperlink ref="D209" r:id="rId127" display="https://www.pbs.org/newshour/politics/trump-administration-admits-legal-errors-and-withdraws-subpoenas-of-3-nyt-reporters"/>
+    <hyperlink ref="D210" r:id="rId128" display="https://www.theguardian.com/commentisfree/2026/jul/24/icc-international-criminal-court-trump-putin-netanyahu"/>
+    <hyperlink ref="D211" r:id="rId129" display="https://www.cbsnews.com/news/trump-smithsonian-museum-warning-signs-inaccurate-information/"/>
+    <hyperlink ref="D212" r:id="rId130" display="https://www.cbsnews.com/news/senate-ice-graphite-spyware-phones/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11048,7 +11370,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1118</v>
+        <v>1140</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -11057,7 +11379,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1119</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11215,7 +11537,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1120</v>
+        <v>1142</v>
       </c>
       <c r="B20" s="10" t="n">
         <f aca="false">SUM(B3:B19)</f>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$205</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$213</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="1143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="1165">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1659,6 +1659,15 @@
     <t xml:space="preserve">Jul 24</t>
   </si>
   <si>
+    <t xml:space="preserve">Jul 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 17</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3445,6 +3454,63 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.cbsnews.com/news/senate-ice-graphite-spyware-phones/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elon Musk likely broke the law by promising voters $1 million payouts, Wisconsin board says</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/elon-musk-broke-law-giving-voters-1-million-134761386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. military will test service members’ testosterone levels, Pete Hegseth says</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/trump-administration/pete-hegseth-says-military-will-test-service-members-testosterone-leve-rcna587682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 15, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump made $1.4bn from crypto in one year. Is Justin Sun the man who helped him do it?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/technology/ng-interactive/2026/jul/16/justin-sun-trump-family-crypto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 16, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump Media to sell faster access to president's Truth Social posts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cbsnews.com/news/truth-api-trump-media/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump calls for new election security measures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/nightly-news/video/trump-calls-for-new-election-security-measures-266865733992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 17, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump has declared war on elections in the name of protecting them | Austin Sarat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/commentisfree/2026/jul/17/trump-speech-election-denialism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump falsely alleges voting machines are "vulnerable" and "easily compromised"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cbsnews.com/news/trump-falsely-alleges-voting-machines-are-vulnerable-and-easily-compromised/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump tries to undermine trust in elections, but documents don't support his claims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/show/trump-tries-to-undermine-trust-in-elections-but-documents-dont-support-his-claims</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -3926,7 +3992,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F205"/>
+  <dimension ref="A1:F213"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -7632,7 +7698,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="5" t="s">
         <v>540</v>
       </c>
@@ -7646,7 +7712,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="5" t="s">
         <v>540</v>
       </c>
@@ -7660,7 +7726,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="5" t="s">
         <v>540</v>
       </c>
@@ -7674,7 +7740,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="5" t="s">
         <v>540</v>
       </c>
@@ -7688,7 +7754,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="5" t="s">
         <v>540</v>
       </c>
@@ -7702,7 +7768,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="5" t="s">
         <v>540</v>
       </c>
@@ -7716,7 +7782,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="5" t="s">
         <v>540</v>
       </c>
@@ -7730,7 +7796,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="5" t="s">
         <v>540</v>
       </c>
@@ -7744,8 +7810,120 @@
         <v>203</v>
       </c>
     </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="C206" s="4"/>
+      <c r="D206" s="4"/>
+      <c r="E206" s="4"/>
+      <c r="F206" s="4" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="C207" s="4"/>
+      <c r="D207" s="4"/>
+      <c r="E207" s="4"/>
+      <c r="F207" s="4" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="C208" s="4"/>
+      <c r="D208" s="4"/>
+      <c r="E208" s="4"/>
+      <c r="F208" s="4" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="C209" s="4"/>
+      <c r="D209" s="4"/>
+      <c r="E209" s="4"/>
+      <c r="F209" s="4" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="C210" s="4"/>
+      <c r="D210" s="4"/>
+      <c r="E210" s="4"/>
+      <c r="F210" s="4" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="C211" s="4"/>
+      <c r="D211" s="4"/>
+      <c r="E211" s="4"/>
+      <c r="F211" s="4" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="C212" s="4"/>
+      <c r="D212" s="4"/>
+      <c r="E212" s="4"/>
+      <c r="F212" s="4" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="C213" s="4"/>
+      <c r="D213" s="4"/>
+      <c r="E213" s="4"/>
+      <c r="F213" s="4" t="n">
+        <v>211</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F205"/>
+  <autoFilter ref="A2:F213"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -7765,7 +7943,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E212"/>
+  <dimension ref="A1:E220"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -7776,7 +7954,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7785,19 +7963,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7805,14 +7983,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7820,14 +7998,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7835,14 +8013,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7850,14 +8028,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7865,14 +8043,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7880,14 +8058,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7895,14 +8073,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7910,14 +8088,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7925,14 +8103,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7940,14 +8118,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7955,14 +8133,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7970,14 +8148,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7985,14 +8163,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8000,14 +8178,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8015,14 +8193,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8030,14 +8208,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8045,14 +8223,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8060,14 +8238,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8075,14 +8253,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8090,14 +8268,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8105,14 +8283,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8120,14 +8298,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8135,14 +8313,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8150,14 +8328,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8165,14 +8343,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8180,14 +8358,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8195,14 +8373,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8210,14 +8388,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8225,14 +8403,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8240,14 +8418,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8255,14 +8433,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8270,14 +8448,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8285,14 +8463,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8300,14 +8478,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8315,14 +8493,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8330,14 +8508,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8345,14 +8523,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8360,14 +8538,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8375,10 +8553,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -8390,14 +8568,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8405,14 +8583,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8420,14 +8598,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8435,14 +8613,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8450,14 +8628,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8465,14 +8643,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8480,14 +8658,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8495,14 +8673,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8510,14 +8688,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8525,14 +8703,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8540,14 +8718,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8555,14 +8733,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8570,14 +8748,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8585,14 +8763,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8600,14 +8778,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8615,14 +8793,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8630,14 +8808,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8645,14 +8823,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8660,14 +8838,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8675,14 +8853,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8690,14 +8868,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8705,14 +8883,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8720,14 +8898,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8735,14 +8913,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8750,14 +8928,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8765,14 +8943,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8780,14 +8958,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8795,14 +8973,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8810,14 +8988,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8825,14 +9003,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8840,14 +9018,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8855,14 +9033,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8870,14 +9048,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8885,14 +9063,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8900,14 +9078,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8915,14 +9093,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8930,14 +9108,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8945,14 +9123,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8960,14 +9138,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8975,14 +9153,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8990,16 +9168,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9007,16 +9185,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9024,13 +9202,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -9041,13 +9219,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -9058,16 +9236,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9075,16 +9253,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9092,16 +9270,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="D88" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>799</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9109,16 +9287,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9126,16 +9304,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9143,16 +9321,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="D91" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>809</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9160,16 +9338,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9177,16 +9355,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D93" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>815</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9194,16 +9372,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9211,16 +9389,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9228,16 +9406,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9245,16 +9423,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>829</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>825</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>826</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>827</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9262,16 +9440,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9279,16 +9457,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9296,16 +9474,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9313,16 +9491,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9330,16 +9508,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9347,16 +9525,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9364,13 +9542,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -9381,16 +9559,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9398,16 +9576,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9415,16 +9593,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9432,16 +9610,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9449,13 +9627,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -9466,13 +9644,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -9483,16 +9661,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9500,16 +9678,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9517,13 +9695,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -9534,16 +9712,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9551,16 +9729,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9568,16 +9746,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9585,16 +9763,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9602,13 +9780,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -9619,16 +9797,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9636,16 +9814,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9653,16 +9831,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9670,16 +9848,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9687,13 +9865,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -9704,13 +9882,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -9721,16 +9899,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9738,16 +9916,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="D126" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="E126" s="5" t="s">
         <v>915</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9755,16 +9933,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9772,16 +9950,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9789,16 +9967,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9806,16 +9984,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C130" s="5" t="s">
+        <v>931</v>
+      </c>
+      <c r="D130" s="6" t="s">
         <v>928</v>
       </c>
-      <c r="D130" s="6" t="s">
-        <v>925</v>
-      </c>
       <c r="E130" s="5" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9823,13 +10001,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -9840,16 +10018,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9857,16 +10035,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="D133" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="E133" s="5" t="s">
         <v>938</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9874,16 +10052,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9891,16 +10069,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9908,13 +10086,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -9925,13 +10103,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -9942,16 +10120,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9959,16 +10137,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9976,13 +10154,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -9993,16 +10171,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10010,16 +10188,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10027,13 +10205,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -10044,16 +10222,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10061,13 +10239,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -10078,16 +10256,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10095,16 +10273,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10112,16 +10290,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10129,13 +10307,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -10146,13 +10324,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -10163,16 +10341,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10180,16 +10358,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10197,16 +10375,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10214,16 +10392,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10231,16 +10409,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10248,16 +10426,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10265,14 +10443,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10280,16 +10458,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="D158" s="6" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E158" s="5" t="s">
         <v>1013</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10297,16 +10475,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10314,16 +10492,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10331,16 +10509,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C161" s="5" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>1019</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>1020</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10348,16 +10526,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10365,16 +10543,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10382,16 +10560,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10399,16 +10577,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10416,13 +10594,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -10433,16 +10611,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10450,13 +10628,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -10467,16 +10645,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10484,16 +10662,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10501,16 +10679,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C171" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>1043</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10518,16 +10696,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10535,16 +10713,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10552,16 +10730,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10569,16 +10747,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C175" s="5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>1053</v>
-      </c>
-      <c r="D175" s="6" t="s">
-        <v>1054</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10586,16 +10764,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10603,16 +10781,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10620,16 +10798,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C178" s="5" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>1060</v>
-      </c>
-      <c r="D178" s="6" t="s">
-        <v>1061</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10637,16 +10815,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10654,16 +10832,16 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10671,16 +10849,16 @@
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10688,16 +10866,16 @@
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10705,16 +10883,16 @@
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10722,16 +10900,16 @@
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C184" s="5" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E184" s="5" t="s">
         <v>1074</v>
-      </c>
-      <c r="D184" s="6" t="s">
-        <v>1075</v>
-      </c>
-      <c r="E184" s="5" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10739,16 +10917,16 @@
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10756,16 +10934,16 @@
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10773,16 +10951,16 @@
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10790,16 +10968,16 @@
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10807,16 +10985,16 @@
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10824,16 +11002,16 @@
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C190" s="5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E190" s="5" t="s">
         <v>1087</v>
-      </c>
-      <c r="D190" s="6" t="s">
-        <v>1088</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10841,16 +11019,16 @@
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10858,16 +11036,16 @@
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10875,13 +11053,13 @@
         <v>184</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>533</v>
@@ -10892,16 +11070,16 @@
         <v>185</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10909,16 +11087,16 @@
         <v>186</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10926,16 +11104,16 @@
         <v>187</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10943,16 +11121,16 @@
         <v>188</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C197" s="5" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E197" s="5" t="s">
         <v>1103</v>
-      </c>
-      <c r="D197" s="6" t="s">
-        <v>1104</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10960,16 +11138,16 @@
         <v>189</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10977,16 +11155,16 @@
         <v>190</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10994,16 +11172,16 @@
         <v>191</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11011,16 +11189,16 @@
         <v>192</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C201" s="5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E201" s="5" t="s">
         <v>1112</v>
-      </c>
-      <c r="D201" s="6" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E201" s="5" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11028,16 +11206,16 @@
         <v>193</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11045,16 +11223,16 @@
         <v>194</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11062,152 +11240,288 @@
         <v>195</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="205" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="5" t="n">
         <v>196</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="E205" s="5" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="5" t="n">
         <v>197</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="5" t="n">
         <v>198</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="208" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="5" t="n">
         <v>199</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C208" s="5" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E208" s="5" t="s">
         <v>1129</v>
       </c>
-      <c r="D208" s="6" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E208" s="5" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="5" t="n">
         <v>200</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="210" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="5" t="n">
         <v>201</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="5" t="n">
         <v>202</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="5" t="n">
         <v>203</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C212" s="5" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E212" s="5" t="s">
         <v>1138</v>
       </c>
-      <c r="D212" s="6" t="s">
-        <v>1139</v>
-      </c>
-      <c r="E212" s="5" t="s">
-        <v>1135</v>
+    </row>
+    <row r="213" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E213" s="5" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E214" s="5" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E215" s="5" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E216" s="5" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E217" s="5" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="5" t="n">
+        <v>209</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E218" s="5" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E219" s="5" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="5" t="n">
+        <v>211</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E220" s="5" t="s">
+        <v>1155</v>
       </c>
     </row>
   </sheetData>
@@ -11345,6 +11659,14 @@
     <hyperlink ref="D210" r:id="rId128" display="https://www.theguardian.com/commentisfree/2026/jul/24/icc-international-criminal-court-trump-putin-netanyahu"/>
     <hyperlink ref="D211" r:id="rId129" display="https://www.cbsnews.com/news/trump-smithsonian-museum-warning-signs-inaccurate-information/"/>
     <hyperlink ref="D212" r:id="rId130" display="https://www.cbsnews.com/news/senate-ice-graphite-spyware-phones/"/>
+    <hyperlink ref="D213" r:id="rId131" display="https://abcnews.com/Politics/wireStory/elon-musk-broke-law-giving-voters-1-million-134761386"/>
+    <hyperlink ref="D214" r:id="rId132" display="https://www.nbcnews.com/politics/trump-administration/pete-hegseth-says-military-will-test-service-members-testosterone-leve-rcna587682"/>
+    <hyperlink ref="D215" r:id="rId133" display="https://www.theguardian.com/technology/ng-interactive/2026/jul/16/justin-sun-trump-family-crypto"/>
+    <hyperlink ref="D216" r:id="rId134" display="https://www.cbsnews.com/news/truth-api-trump-media/"/>
+    <hyperlink ref="D217" r:id="rId135" display="https://www.nbcnews.com/nightly-news/video/trump-calls-for-new-election-security-measures-266865733992"/>
+    <hyperlink ref="D218" r:id="rId136" display="https://www.theguardian.com/commentisfree/2026/jul/17/trump-speech-election-denialism"/>
+    <hyperlink ref="D219" r:id="rId137" display="https://www.cbsnews.com/news/trump-falsely-alleges-voting-machines-are-vulnerable-and-easily-compromised/"/>
+    <hyperlink ref="D220" r:id="rId138" display="https://www.pbs.org/newshour/show/trump-tries-to-undermine-trust-in-elections-but-documents-dont-support-his-claims"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11370,7 +11692,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1140</v>
+        <v>1162</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -11379,7 +11701,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1141</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11537,7 +11859,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1142</v>
+        <v>1164</v>
       </c>
       <c r="B20" s="10" t="n">
         <f aca="false">SUM(B3:B19)</f>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$213</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$222</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="1165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="1190">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1668,6 +1668,18 @@
     <t xml:space="preserve">Jul 17</t>
   </si>
   <si>
+    <t xml:space="preserve">Aug 24, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 28</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3511,6 +3523,69 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.pbs.org/newshour/show/trump-tries-to-undermine-trust-in-elections-but-documents-dont-support-his-claims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Democratic states file new lawsuit seeking to block Trump’s order limiting mail voting in midterms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/democratic-states-file-new-lawsuit-seeking-block-trumps-135974009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 26, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump signs executive order to rename Lake Ontario as ‘Lake America’</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/trump-administration/trump-orders-lake-ontario-renamed-lake-america-canada-trade-war-rcna594750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 27, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group of Democratic senators calls on ICE to cancel plan to buy electric shock gloves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/group-democratic-senators-calls-ice-cancel-plan-buy-136008188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US goals have shifted after 6 months of Iran war. The Strait of Hormuz is now a top concern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/us-goals-shifted-after-6-months-iran-war-135995683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan. 6 rioters pursue new path for payments from Trump administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/show/jan-6-rioters-pursue-new-path-for-payments-from-trump-administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump administration proposal would allow federal grants to be terminated on a whim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.npr.org/2026/08/28/nx-s1-5943238/trump-administration-proposal-would-allow-federal-grants-to-be-terminated-on-a-whim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 28, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump signs order to create space-focused military academy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/trump-administration/trump-space-academy-nasa-military-rcna594870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How did Trump get so rich? | Politics Weekly America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.theguardian.com/politics/video/2026/aug/27/how-did-trump-get-so-rich-politics-weekly-america</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. targets Egyptian bank's UAE branches under new push for Iran's economic isolation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pbs.org/newshour/world/u-s-targets-egyptian-banks-uae-branches-under-new-push-for-irans-economic-isolation</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -3992,7 +4067,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F213"/>
+  <dimension ref="A1:F222"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -7810,7 +7885,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="4" t="s">
         <v>521</v>
       </c>
@@ -7824,7 +7899,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="4" t="s">
         <v>521</v>
       </c>
@@ -7838,7 +7913,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="4" t="s">
         <v>521</v>
       </c>
@@ -7852,7 +7927,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="4" t="s">
         <v>521</v>
       </c>
@@ -7866,7 +7941,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="4" t="s">
         <v>521</v>
       </c>
@@ -7880,7 +7955,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="4" t="s">
         <v>521</v>
       </c>
@@ -7894,7 +7969,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="4" t="s">
         <v>521</v>
       </c>
@@ -7908,7 +7983,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="4" t="s">
         <v>521</v>
       </c>
@@ -7922,8 +7997,150 @@
         <v>211</v>
       </c>
     </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D214" s="5"/>
+      <c r="E214" s="5"/>
+      <c r="F214" s="5" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D215" s="5"/>
+      <c r="E215" s="5"/>
+      <c r="F215" s="5" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D216" s="5"/>
+      <c r="E216" s="5"/>
+      <c r="F216" s="5" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D217" s="5"/>
+      <c r="E217" s="5"/>
+      <c r="F217" s="5" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D218" s="5"/>
+      <c r="E218" s="5"/>
+      <c r="F218" s="5" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D219" s="5"/>
+      <c r="E219" s="5"/>
+      <c r="F219" s="5" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D220" s="5"/>
+      <c r="E220" s="5"/>
+      <c r="F220" s="5" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D221" s="5"/>
+      <c r="E221" s="5"/>
+      <c r="F221" s="5" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="C222" s="5"/>
+      <c r="D222" s="5"/>
+      <c r="E222" s="5"/>
+      <c r="F222" s="5" t="n">
+        <v>220</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F213"/>
+  <autoFilter ref="A2:F222"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -7943,7 +8160,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E220"/>
+  <dimension ref="A1:E229"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -7954,7 +8171,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7963,19 +8180,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7983,14 +8200,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7998,14 +8215,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8013,14 +8230,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8028,14 +8245,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8043,14 +8260,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8058,14 +8275,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8073,14 +8290,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8088,14 +8305,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8103,14 +8320,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8118,14 +8335,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8133,14 +8350,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8148,14 +8365,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8163,14 +8380,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8178,14 +8395,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8193,14 +8410,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8208,14 +8425,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8223,14 +8440,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8238,14 +8455,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8253,14 +8470,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8268,14 +8485,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8283,14 +8500,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8298,14 +8515,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8313,14 +8530,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8328,14 +8545,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8343,14 +8560,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8358,14 +8575,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8373,14 +8590,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8388,14 +8605,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8403,14 +8620,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8418,14 +8635,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8433,14 +8650,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8448,14 +8665,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8463,14 +8680,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8478,14 +8695,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8493,14 +8710,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8508,14 +8725,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8523,14 +8740,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8538,14 +8755,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8553,10 +8770,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -8568,14 +8785,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8583,14 +8800,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8598,14 +8815,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8613,14 +8830,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8628,14 +8845,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8643,14 +8860,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8658,14 +8875,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8673,14 +8890,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8688,14 +8905,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8703,14 +8920,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8718,14 +8935,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8733,14 +8950,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8748,14 +8965,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8763,14 +8980,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8778,14 +8995,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8793,14 +9010,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8808,14 +9025,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8823,14 +9040,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8838,14 +9055,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8853,14 +9070,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8868,14 +9085,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8883,14 +9100,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8898,14 +9115,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8913,14 +9130,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8928,14 +9145,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8943,14 +9160,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8958,14 +9175,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8973,14 +9190,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8988,14 +9205,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9003,14 +9220,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9018,14 +9235,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9033,14 +9250,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9048,14 +9265,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9063,14 +9280,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9078,14 +9295,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9093,14 +9310,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9108,14 +9325,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9123,14 +9340,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9138,14 +9355,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9153,14 +9370,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9168,16 +9385,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9185,16 +9402,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9202,13 +9419,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -9219,13 +9436,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -9236,16 +9453,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9253,16 +9470,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9270,16 +9487,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9287,16 +9504,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>803</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>805</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9304,16 +9521,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9321,16 +9538,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9338,16 +9555,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9355,16 +9572,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9372,16 +9589,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9389,16 +9606,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9406,16 +9623,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9423,16 +9640,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="C97" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>829</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>830</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9440,16 +9657,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9457,16 +9674,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9474,16 +9691,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9491,16 +9708,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9508,16 +9725,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9525,16 +9742,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9542,13 +9759,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -9559,16 +9776,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9576,16 +9793,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9593,16 +9810,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9610,16 +9827,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9627,13 +9844,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -9644,13 +9861,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -9661,16 +9878,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9678,16 +9895,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9695,13 +9912,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -9712,16 +9929,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9729,16 +9946,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9746,16 +9963,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9763,16 +9980,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9780,13 +9997,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -9797,16 +10014,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9814,16 +10031,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9831,16 +10048,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="E121" s="5" t="s">
         <v>902</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>903</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>904</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9848,16 +10065,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9865,13 +10082,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -9882,13 +10099,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -9899,16 +10116,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9916,16 +10133,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9933,16 +10150,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9950,16 +10167,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9967,16 +10184,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9984,16 +10201,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10001,13 +10218,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -10018,16 +10235,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10035,16 +10252,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10052,16 +10269,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10069,16 +10286,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10086,13 +10303,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -10103,13 +10320,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -10120,16 +10337,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10137,16 +10354,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10154,13 +10371,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -10171,16 +10388,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10188,16 +10405,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10205,13 +10422,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -10222,16 +10439,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10239,13 +10456,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -10256,16 +10473,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10273,16 +10490,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10290,16 +10507,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10307,13 +10524,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -10324,13 +10541,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -10341,16 +10558,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10358,16 +10575,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10375,16 +10592,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10392,16 +10609,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10409,16 +10626,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10426,16 +10643,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10443,14 +10660,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10458,16 +10675,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10475,16 +10692,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10492,16 +10709,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10509,16 +10726,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="D161" s="6" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>1023</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10526,16 +10743,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10543,16 +10760,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10560,16 +10777,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10577,16 +10794,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10594,13 +10811,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -10611,16 +10828,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10628,13 +10845,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -10645,16 +10862,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10662,16 +10879,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10679,16 +10896,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="D171" s="6" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>1047</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10696,16 +10913,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10713,16 +10930,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10730,16 +10947,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10747,16 +10964,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="D175" s="6" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>1057</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10764,16 +10981,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10781,16 +10998,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10798,16 +11015,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="D178" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>1064</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10815,16 +11032,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10832,16 +11049,16 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10849,16 +11066,16 @@
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10866,16 +11083,16 @@
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10883,16 +11100,16 @@
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10900,16 +11117,16 @@
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="D184" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E184" s="5" t="s">
         <v>1078</v>
-      </c>
-      <c r="E184" s="5" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10917,16 +11134,16 @@
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10934,16 +11151,16 @@
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10951,16 +11168,16 @@
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10968,16 +11185,16 @@
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10985,16 +11202,16 @@
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11002,16 +11219,16 @@
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="D190" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E190" s="5" t="s">
         <v>1091</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11019,16 +11236,16 @@
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11036,16 +11253,16 @@
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11053,13 +11270,13 @@
         <v>184</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>533</v>
@@ -11070,16 +11287,16 @@
         <v>185</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11087,16 +11304,16 @@
         <v>186</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11104,16 +11321,16 @@
         <v>187</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11121,16 +11338,16 @@
         <v>188</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="D197" s="6" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E197" s="5" t="s">
         <v>1107</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11138,16 +11355,16 @@
         <v>189</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11155,16 +11372,16 @@
         <v>190</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11172,16 +11389,16 @@
         <v>191</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11189,16 +11406,16 @@
         <v>192</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="D201" s="6" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E201" s="5" t="s">
         <v>1116</v>
-      </c>
-      <c r="E201" s="5" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11206,16 +11423,16 @@
         <v>193</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11223,16 +11440,16 @@
         <v>194</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11240,16 +11457,16 @@
         <v>195</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11257,13 +11474,13 @@
         <v>196</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="E205" s="5" t="s">
         <v>540</v>
@@ -11274,16 +11491,16 @@
         <v>197</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11291,16 +11508,16 @@
         <v>198</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11308,16 +11525,16 @@
         <v>199</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="D208" s="6" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E208" s="5" t="s">
         <v>1133</v>
-      </c>
-      <c r="E208" s="5" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11325,16 +11542,16 @@
         <v>200</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11342,16 +11559,16 @@
         <v>201</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11359,16 +11576,16 @@
         <v>202</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11376,152 +11593,305 @@
         <v>203</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="D212" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E212" s="5" t="s">
         <v>1142</v>
       </c>
-      <c r="E212" s="5" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="213" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="5" t="n">
         <v>204</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="5" t="n">
         <v>205</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="215" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="5" t="n">
         <v>206</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="5" t="n">
         <v>207</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="5" t="n">
         <v>208</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="5" t="n">
         <v>209</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="5" t="n">
         <v>210</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="D219" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E219" s="5" t="s">
         <v>1159</v>
       </c>
-      <c r="E219" s="5" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="5" t="n">
         <v>211</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>1155</v>
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="5" t="n">
+        <v>213</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="C222" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E222" s="5" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E223" s="5" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E224" s="5" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E225" s="5" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E226" s="5" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E227" s="5" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="5" t="n">
+        <v>219</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E228" s="5" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D229" s="6" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E229" s="5" t="s">
+        <v>1180</v>
       </c>
     </row>
   </sheetData>
@@ -11667,6 +12037,15 @@
     <hyperlink ref="D218" r:id="rId136" display="https://www.theguardian.com/commentisfree/2026/jul/17/trump-speech-election-denialism"/>
     <hyperlink ref="D219" r:id="rId137" display="https://www.cbsnews.com/news/trump-falsely-alleges-voting-machines-are-vulnerable-and-easily-compromised/"/>
     <hyperlink ref="D220" r:id="rId138" display="https://www.pbs.org/newshour/show/trump-tries-to-undermine-trust-in-elections-but-documents-dont-support-his-claims"/>
+    <hyperlink ref="D221" r:id="rId139" display="https://abcnews.com/Politics/wireStory/democratic-states-file-new-lawsuit-seeking-block-trumps-135974009"/>
+    <hyperlink ref="D222" r:id="rId140" display="https://www.nbcnews.com/politics/trump-administration/trump-orders-lake-ontario-renamed-lake-america-canada-trade-war-rcna594750"/>
+    <hyperlink ref="D223" r:id="rId141" display="https://abcnews.com/Politics/wireStory/group-democratic-senators-calls-ice-cancel-plan-buy-136008188"/>
+    <hyperlink ref="D224" r:id="rId142" display="https://abcnews.com/Politics/wireStory/us-goals-shifted-after-6-months-iran-war-135995683"/>
+    <hyperlink ref="D225" r:id="rId143" display="https://www.pbs.org/newshour/show/jan-6-rioters-pursue-new-path-for-payments-from-trump-administration"/>
+    <hyperlink ref="D226" r:id="rId144" display="https://www.npr.org/2026/08/28/nx-s1-5943238/trump-administration-proposal-would-allow-federal-grants-to-be-terminated-on-a-whim"/>
+    <hyperlink ref="D227" r:id="rId145" display="https://www.nbcnews.com/politics/trump-administration/trump-space-academy-nasa-military-rcna594870"/>
+    <hyperlink ref="D228" r:id="rId146" display="https://www.theguardian.com/politics/video/2026/aug/27/how-did-trump-get-so-rich-politics-weekly-america"/>
+    <hyperlink ref="D229" r:id="rId147" display="https://www.pbs.org/newshour/world/u-s-targets-egyptian-banks-uae-branches-under-new-push-for-irans-economic-isolation"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11692,7 +12071,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1162</v>
+        <v>1187</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -11701,7 +12080,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1163</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11710,7 +12089,7 @@
       </c>
       <c r="B3" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A3)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11728,7 +12107,7 @@
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A5)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11737,7 +12116,7 @@
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A6)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11746,7 +12125,7 @@
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A7)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11773,7 +12152,7 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A10)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11791,7 +12170,7 @@
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A12)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11859,11 +12238,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1164</v>
+        <v>1189</v>
       </c>
       <c r="B20" s="10" t="n">
         <f aca="false">SUM(B3:B19)</f>
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/data/Trump_Second_Term_Weekly_Tracker.xlsx
+++ b/data/Trump_Second_Term_Weekly_Tracker.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$222</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Weekly Timeline'!$A$2:$F$226</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="1204">
   <si>
     <t xml:space="preserve">Documented actions and policies of the second Trump administration reported as harmful by major news outlets, courts, and government data — Jan 20, 2025 through Jul 8, 2026. One row per event; weeks with multiple events have multiple rows; quiet weeks are skipped. This compiles critical coverage as requested; the administration and its supporters dispute many of these characterizations. See the Sources tab (matching Ref #) and verify details independently before citing.</t>
   </si>
@@ -1680,6 +1680,18 @@
     <t xml:space="preserve">Aug 28</t>
   </si>
   <si>
+    <t xml:space="preserve">Aug 31, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and History</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref # matches the Source Ref column on the Weekly Timeline tab. URLs are provided where verified via current web results (mostly 2026 items). For 2025 items, outlet names and dates are given; searching the description text will locate the original coverage. Per your request the mix emphasizes CNN, Politico, MSNBC/MS NOW, NBC and independent outlets, alongside AP, Reuters, Guardian, NPR, CBS, ABC and court documents.</t>
   </si>
   <si>
@@ -3586,6 +3598,36 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.pbs.org/newshour/world/u-s-targets-egyptian-banks-uae-branches-under-new-push-for-irans-economic-isolation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOJ asks Supreme Court to allow Trump’s USPS action on mail-in ballots to proceed ahead of midterm elections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/trump-administration/justice-department-usps-supreme-court-action-mail-ballots-elections-rcna595924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 3, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excavation work on Trump's arch in Washington to begin over next 2 weeks, administration says</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://abcnews.com/Politics/wireStory/excavation-work-trumps-arch-washington-begin-2-weeks-136185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump administration rolls out 5 voter fraud prosecutions ahead of midterms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nbcnews.com/politics/justice-department/trump-administration-rolls-5-voter-fraud-prosecutions-ahead-midterms-rcna596089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 4, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judge lets Pentagon move forward with firing Stars and Stripes journalists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cbsnews.com/news/judge-allows-pentagon-fire-stars-stripes-journalists/</t>
   </si>
   <si>
     <t xml:space="preserve">Entries by category (live COUNTIF formulas against the Weekly Timeline tab)</t>
@@ -3774,7 +3816,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4067,7 +4109,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F222"/>
+  <dimension ref="A1:F226"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.01"/>
@@ -7997,7 +8039,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="5" t="s">
         <v>547</v>
       </c>
@@ -8013,7 +8055,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="5" t="s">
         <v>547</v>
       </c>
@@ -8029,7 +8071,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="5" t="s">
         <v>547</v>
       </c>
@@ -8045,7 +8087,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="5" t="s">
         <v>547</v>
       </c>
@@ -8061,7 +8103,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="5" t="s">
         <v>547</v>
       </c>
@@ -8077,7 +8119,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="5" t="s">
         <v>547</v>
       </c>
@@ -8093,7 +8135,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="5" t="s">
         <v>547</v>
       </c>
@@ -8109,7 +8151,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="5" t="s">
         <v>547</v>
       </c>
@@ -8125,7 +8167,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="5" t="s">
         <v>547</v>
       </c>
@@ -8139,8 +8181,72 @@
         <v>220</v>
       </c>
     </row>
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D223" s="4"/>
+      <c r="E223" s="4"/>
+      <c r="F223" s="4" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="D224" s="4"/>
+      <c r="E224" s="4"/>
+      <c r="F224" s="4" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D225" s="4"/>
+      <c r="E225" s="4"/>
+      <c r="F225" s="4" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" s="4"/>
+      <c r="E226" s="4"/>
+      <c r="F226" s="4" t="n">
+        <v>224</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F222"/>
+  <autoFilter ref="A2:F226"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -8160,7 +8266,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E229"/>
+  <dimension ref="A1:E233"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -8171,7 +8277,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8180,19 +8286,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8200,14 +8306,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8215,14 +8321,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8230,14 +8336,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8245,14 +8351,14 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8260,14 +8366,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8275,14 +8381,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8290,14 +8396,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8305,14 +8411,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8320,14 +8426,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8335,14 +8441,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8350,14 +8456,14 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8365,14 +8471,14 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8380,14 +8486,14 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8395,14 +8501,14 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8410,14 +8516,14 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8425,14 +8531,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8440,14 +8546,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8455,14 +8561,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8470,14 +8576,14 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8485,14 +8591,14 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8500,14 +8606,14 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8515,14 +8621,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8530,14 +8636,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8545,14 +8651,14 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8560,14 +8666,14 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8575,14 +8681,14 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8590,14 +8696,14 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8605,14 +8711,14 @@
         <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8620,14 +8726,14 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8635,14 +8741,14 @@
         <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8650,14 +8756,14 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8665,14 +8771,14 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8680,14 +8786,14 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8695,14 +8801,14 @@
         <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8710,14 +8816,14 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8725,14 +8831,14 @@
         <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8740,14 +8846,14 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8755,14 +8861,14 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8770,10 +8876,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
@@ -8785,14 +8891,14 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8800,14 +8906,14 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8815,14 +8921,14 @@
         <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8830,14 +8936,14 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8845,14 +8951,14 @@
         <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8860,14 +8966,14 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8875,14 +8981,14 @@
         <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8890,14 +8996,14 @@
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8905,14 +9011,14 @@
         <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8920,14 +9026,14 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8935,14 +9041,14 @@
         <v>50</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8950,14 +9056,14 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8965,14 +9071,14 @@
         <v>52</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8980,14 +9086,14 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8995,14 +9101,14 @@
         <v>54</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9010,14 +9116,14 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9025,14 +9131,14 @@
         <v>56</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9040,14 +9146,14 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9055,14 +9161,14 @@
         <v>58</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9070,14 +9176,14 @@
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9085,14 +9191,14 @@
         <v>60</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9100,14 +9206,14 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9115,14 +9221,14 @@
         <v>62</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9130,14 +9236,14 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9145,14 +9251,14 @@
         <v>64</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9160,14 +9266,14 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9175,14 +9281,14 @@
         <v>66</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9190,14 +9296,14 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9205,14 +9311,14 @@
         <v>68</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9220,14 +9326,14 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9235,14 +9341,14 @@
         <v>70</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9250,14 +9356,14 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9265,14 +9371,14 @@
         <v>72</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9280,14 +9386,14 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9295,14 +9401,14 @@
         <v>74</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9310,14 +9416,14 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="5" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9325,14 +9431,14 @@
         <v>76</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="5" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9340,14 +9446,14 @@
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9355,14 +9461,14 @@
         <v>78</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9370,14 +9476,14 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9385,16 +9491,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9402,16 +9508,16 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9419,13 +9525,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>297</v>
@@ -9436,13 +9542,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>300</v>
@@ -9453,16 +9559,16 @@
         <v>84</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9470,16 +9576,16 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9487,16 +9593,16 @@
         <v>86</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9504,16 +9610,16 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>807</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>808</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>809</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9521,16 +9627,16 @@
         <v>88</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9538,16 +9644,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9555,16 +9661,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9572,16 +9678,16 @@
         <v>91</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9589,16 +9695,16 @@
         <v>92</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9606,16 +9712,16 @@
         <v>93</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9623,16 +9729,16 @@
         <v>94</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9640,16 +9746,16 @@
         <v>95</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C97" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>833</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>834</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9657,16 +9763,16 @@
         <v>96</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9674,16 +9780,16 @@
         <v>97</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9691,16 +9797,16 @@
         <v>98</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9708,16 +9814,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9725,16 +9831,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9742,16 +9848,16 @@
         <v>101</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9759,13 +9865,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>352</v>
@@ -9776,16 +9882,16 @@
         <v>103</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9793,16 +9899,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9810,16 +9916,16 @@
         <v>105</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9827,16 +9933,16 @@
         <v>106</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9844,13 +9950,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>368</v>
@@ -9861,13 +9967,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>368</v>
@@ -9878,16 +9984,16 @@
         <v>109</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9895,16 +10001,16 @@
         <v>110</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9912,13 +10018,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>382</v>
@@ -9929,16 +10035,16 @@
         <v>112</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9946,16 +10052,16 @@
         <v>113</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9963,16 +10069,16 @@
         <v>114</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9980,16 +10086,16 @@
         <v>115</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9997,13 +10103,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>396</v>
@@ -10014,16 +10120,16 @@
         <v>117</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10031,16 +10137,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10048,16 +10154,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="E121" s="5" t="s">
         <v>906</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>907</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>908</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10065,16 +10171,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10082,13 +10188,13 @@
         <v>121</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>409</v>
@@ -10099,13 +10205,13 @@
         <v>122</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>409</v>
@@ -10116,16 +10222,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10133,16 +10239,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10150,16 +10256,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10167,16 +10273,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10184,16 +10290,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10201,16 +10307,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10218,13 +10324,13 @@
         <v>129</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>434</v>
@@ -10235,16 +10341,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10252,16 +10358,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10269,16 +10375,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10286,16 +10392,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10303,13 +10409,13 @@
         <v>134</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>451</v>
@@ -10320,13 +10426,13 @@
         <v>135</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>451</v>
@@ -10337,16 +10443,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10354,16 +10460,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10371,13 +10477,13 @@
         <v>138</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>463</v>
@@ -10388,16 +10494,16 @@
         <v>139</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10405,16 +10511,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10422,13 +10528,13 @@
         <v>141</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>472</v>
@@ -10439,16 +10545,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10456,13 +10562,13 @@
         <v>143</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>479</v>
@@ -10473,16 +10579,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10490,16 +10596,16 @@
         <v>145</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10507,16 +10613,16 @@
         <v>146</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10524,13 +10630,13 @@
         <v>147</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>492</v>
@@ -10541,13 +10647,13 @@
         <v>148</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>492</v>
@@ -10558,16 +10664,16 @@
         <v>149</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10575,16 +10681,16 @@
         <v>150</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10592,16 +10698,16 @@
         <v>151</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10609,16 +10715,16 @@
         <v>152</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10626,16 +10732,16 @@
         <v>153</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10643,16 +10749,16 @@
         <v>154</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10660,14 +10766,14 @@
         <v>155</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10675,16 +10781,16 @@
         <v>156</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10692,16 +10798,16 @@
         <v>157</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10709,16 +10815,16 @@
         <v>158</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10726,16 +10832,16 @@
         <v>159</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="D161" s="6" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>1027</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10743,16 +10849,16 @@
         <v>160</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10760,16 +10866,16 @@
         <v>161</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10777,16 +10883,16 @@
         <v>162</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10794,16 +10900,16 @@
         <v>163</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10811,13 +10917,13 @@
         <v>157</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>521</v>
@@ -10828,16 +10934,16 @@
         <v>158</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10845,13 +10951,13 @@
         <v>159</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>524</v>
@@ -10862,16 +10968,16 @@
         <v>160</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10879,16 +10985,16 @@
         <v>161</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10896,16 +11002,16 @@
         <v>162</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="D171" s="6" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>1051</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10913,16 +11019,16 @@
         <v>163</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10930,16 +11036,16 @@
         <v>164</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10947,16 +11053,16 @@
         <v>165</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10964,16 +11070,16 @@
         <v>166</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="D175" s="6" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>1061</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10981,16 +11087,16 @@
         <v>167</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10998,16 +11104,16 @@
         <v>168</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11015,16 +11121,16 @@
         <v>169</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="D178" s="6" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>1068</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11032,16 +11138,16 @@
         <v>170</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11049,16 +11155,16 @@
         <v>171</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11066,16 +11172,16 @@
         <v>172</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11083,16 +11189,16 @@
         <v>173</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11100,16 +11206,16 @@
         <v>174</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11117,16 +11223,16 @@
         <v>175</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="D184" s="6" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E184" s="5" t="s">
         <v>1082</v>
-      </c>
-      <c r="E184" s="5" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11134,16 +11240,16 @@
         <v>176</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11151,16 +11257,16 @@
         <v>177</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11168,16 +11274,16 @@
         <v>178</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11185,16 +11291,16 @@
         <v>179</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11202,16 +11308,16 @@
         <v>180</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11219,16 +11325,16 @@
         <v>181</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="D190" s="6" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E190" s="5" t="s">
         <v>1095</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11236,16 +11342,16 @@
         <v>182</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11253,16 +11359,16 @@
         <v>183</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11270,13 +11376,13 @@
         <v>184</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>533</v>
@@ -11287,16 +11393,16 @@
         <v>185</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11304,16 +11410,16 @@
         <v>186</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11321,16 +11427,16 @@
         <v>187</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11338,16 +11444,16 @@
         <v>188</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="D197" s="6" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E197" s="5" t="s">
         <v>1111</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11355,16 +11461,16 @@
         <v>189</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11372,16 +11478,16 @@
         <v>190</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11389,16 +11495,16 @@
         <v>191</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11406,16 +11512,16 @@
         <v>192</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="D201" s="6" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E201" s="5" t="s">
         <v>1120</v>
-      </c>
-      <c r="E201" s="5" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11423,16 +11529,16 @@
         <v>193</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11440,16 +11546,16 @@
         <v>194</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11457,16 +11563,16 @@
         <v>195</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11474,13 +11580,13 @@
         <v>196</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="E205" s="5" t="s">
         <v>540</v>
@@ -11491,16 +11597,16 @@
         <v>197</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11508,16 +11614,16 @@
         <v>198</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11525,16 +11631,16 @@
         <v>199</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="D208" s="6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E208" s="5" t="s">
         <v>1137</v>
-      </c>
-      <c r="E208" s="5" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11542,16 +11648,16 @@
         <v>200</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11559,16 +11665,16 @@
         <v>201</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11576,16 +11682,16 @@
         <v>202</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11593,16 +11699,16 @@
         <v>203</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="D212" s="6" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E212" s="5" t="s">
         <v>1146</v>
-      </c>
-      <c r="E212" s="5" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11610,16 +11716,16 @@
         <v>204</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11627,16 +11733,16 @@
         <v>205</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11644,16 +11750,16 @@
         <v>206</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11661,16 +11767,16 @@
         <v>207</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11678,16 +11784,16 @@
         <v>208</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11695,16 +11801,16 @@
         <v>209</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11712,16 +11818,16 @@
         <v>210</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="D219" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E219" s="5" t="s">
         <v>1163</v>
-      </c>
-      <c r="E219" s="5" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11729,169 +11835,237 @@
         <v>211</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="5" t="n">
         <v>212</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>1168</v>
-      </c>
-    </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="5" t="n">
         <v>213</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="5" t="n">
         <v>214</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="224" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="5" t="n">
         <v>215</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="D224" s="6" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E224" s="5" t="s">
         <v>1175</v>
       </c>
-      <c r="E224" s="5" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="5" t="n">
         <v>216</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="5" t="n">
         <v>217</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="5" t="n">
         <v>218</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="5" t="n">
         <v>219</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="D228" s="6" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E228" s="5" t="s">
         <v>1184</v>
       </c>
-      <c r="E228" s="5" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="229" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="5" t="n">
         <v>220</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>1180</v>
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="5" t="n">
+        <v>221</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D230" s="6" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E230" s="5" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="5" t="n">
+        <v>222</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D231" s="6" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E231" s="5" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D232" s="6" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E232" s="5" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D233" s="6" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E233" s="5" t="s">
+        <v>1198</v>
       </c>
     </row>
   </sheetData>
@@ -12046,6 +12220,10 @@
     <hyperlink ref="D227" r:id="rId145" display="https://www.nbcnews.com/politics/trump-administration/trump-space-academy-nasa-military-rcna594870"/>
     <hyperlink ref="D228" r:id="rId146" display="https://www.theguardian.com/politics/video/2026/aug/27/how-did-trump-get-so-rich-politics-weekly-america"/>
     <hyperlink ref="D229" r:id="rId147" display="https://www.pbs.org/newshour/world/u-s-targets-egyptian-banks-uae-branches-under-new-push-for-irans-economic-isolation"/>
+    <hyperlink ref="D230" r:id="rId148" display="https://www.nbcnews.com/politics/trump-administration/justice-department-usps-supreme-court-action-mail-ballots-elections-rcna595924"/>
+    <hyperlink ref="D231" r:id="rId149" display="https://abcnews.com/Politics/wireStory/excavation-work-trumps-arch-washington-begin-2-weeks-136185425"/>
+    <hyperlink ref="D232" r:id="rId150" display="https://www.nbcnews.com/politics/justice-department/trump-administration-rolls-5-voter-fraud-prosecutions-ahead-midterms-rcna596089"/>
+    <hyperlink ref="D233" r:id="rId151" display="https://www.cbsnews.com/news/judge-allows-pentagon-fire-stars-stripes-journalists/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12062,7 +12240,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.01"/>
@@ -12071,7 +12249,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1187</v>
+        <v>1201</v>
       </c>
       <c r="B1" s="7"/>
     </row>
@@ -12080,7 +12258,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1188</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12116,7 +12294,7 @@
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A6)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12202,47 +12380,56 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>15</v>
+        <v>553</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A16)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A17)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A18)</f>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>346</v>
+        <v>72</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">COUNTIF('Weekly Timeline'!C:C,A19)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <f aca="false">COUNTIF('Weekly Timeline'!C:C,A20)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
-        <v>1189</v>
-      </c>
-      <c r="B20" s="10" t="n">
-        <f aca="false">SUM(B3:B19)</f>
-        <v>164</v>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B21" s="10" t="n">
+        <f aca="false">SUM(B3:B20)</f>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
